--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,27 +603,27 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>112232</v>
+        <v>112239</v>
       </c>
       <c r="C3" t="n">
-        <v>262903</v>
+        <v>387765</v>
       </c>
       <c r="D3" t="n">
-        <v>60407</v>
+        <v>29922</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAUL  ZUÑIGA MARTINEZ</t>
+          <t>GABRIELA NICOLE INZUNZA VILLARREAL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>01-10-2026 5:44:16</t>
+          <t>01-10-2026 9:06:03</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -645,17 +645,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>549</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>999</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>26-09-2027 9:06:03</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -800,27 +802,27 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>110227</v>
+        <v>112232</v>
       </c>
       <c r="C6" t="n">
-        <v>382358</v>
+        <v>262903</v>
       </c>
       <c r="D6" t="n">
-        <v>24515</v>
+        <v>60407</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MARISOL  ACUÑA VAZQUEZ</t>
+          <t>RAUL  ZUÑIGA MARTINEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>03-09-2026 21:18:41</t>
+          <t>01-10-2026 5:44:16</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -838,11 +840,11 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -855,9 +857,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P6" t="n">
-        <v>110080</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -865,29 +865,27 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>110818</v>
+        <v>112246</v>
       </c>
       <c r="C7" t="n">
-        <v>312013</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>09512</t>
-        </is>
+        <v>386941</v>
+      </c>
+      <c r="D7" t="n">
+        <v>29098</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JESUS GUSTAVO MARQUEZ GONZALEZ</t>
+          <t>FABIOLA  PLAZA  CARMONA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14-09-2026 15:17:57</t>
+          <t>01-10-2026 11:04:12</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -905,18 +903,18 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>499</v>
+        <v>849</v>
       </c>
       <c r="M7" t="n">
         <v>11</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>09-09-2027 15:17:57</t>
+          <t>26-09-2027 11:04:12</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -924,9 +922,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P7" t="n">
-        <v>76787</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -934,29 +930,27 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110106</v>
+        <v>112243</v>
       </c>
       <c r="C8" t="n">
-        <v>204657</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>02165</t>
-        </is>
+        <v>118726</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16436</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ERANDI LIZBETH CRUZ  CASTILLO</t>
+          <t>JONATHAN BERNAL REYNA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>02-09-2026 13:25:36</t>
+          <t>01-10-2026 9:47:38</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -974,18 +968,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>399</v>
+        <v>599</v>
       </c>
       <c r="M8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>28-08-2027 13:25:36</t>
+          <t>30-03-2027 9:47:38</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -993,9 +987,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>7977</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1003,27 +995,27 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>112187</v>
+        <v>110227</v>
       </c>
       <c r="C9" t="n">
-        <v>164685</v>
+        <v>382358</v>
       </c>
       <c r="D9" t="n">
-        <v>62218</v>
+        <v>24515</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OSCAR EDCARDA GUZMAN GONZALEZ</t>
+          <t>MARISOL  ACUÑA VAZQUEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>30-09-2026 15:16:45</t>
+          <t>03-09-2026 21:18:41</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1045,7 +1037,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1059,7 +1051,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>102910</v>
+        <v>110080</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
@@ -1068,32 +1060,32 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>111012</v>
+        <v>112244</v>
       </c>
       <c r="C10" t="n">
-        <v>68471</v>
+        <v>157095</v>
       </c>
       <c r="D10" t="n">
-        <v>66299</v>
+        <v>54639</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JESUS MAURICIO VALTIERRA HERNANDEZ</t>
+          <t>MARIA DE LOURDES ALVARES PADILLA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15-09-2026 19:54:08</t>
+          <t>01-10-2026 10:15:02</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>30-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1110,14 +1102,14 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>499</v>
+        <v>399</v>
       </c>
       <c r="M10" t="n">
         <v>11</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10-09-2027 19:54:08</t>
+          <t>26-09-2027 10:15:02</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1126,7 +1118,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>102987</v>
+        <v>4233</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -1135,17 +1127,17 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>112234</v>
+        <v>112251</v>
       </c>
       <c r="C11" t="n">
-        <v>386565</v>
+        <v>387791</v>
       </c>
       <c r="D11" t="n">
-        <v>28722</v>
+        <v>29948</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JOSE ARMANDO BARAJAS GONGORA</t>
+          <t>ANGEL GABRIEL RIVERA SALAZAR</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1155,7 +1147,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01-10-2026 6:16:40</t>
+          <t>01-10-2026 12:36:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1177,44 +1169,960 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>949</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>849</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>26-09-2027 12:36:00</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Reporte generado: 01-10-2026 02:31 p. m.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>112248</v>
+      </c>
+      <c r="C12" t="n">
+        <v>67098</v>
+      </c>
+      <c r="D12" t="n">
+        <v>64929</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>JARI BLANCARTE CASTRO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>01-10-2026 11:45:13</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>599</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>30-03-2027 11:45:13</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>112240</v>
+      </c>
+      <c r="C13" t="n">
+        <v>326427</v>
+      </c>
+      <c r="D13" t="n">
+        <v>23366</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ANABEL GÓMEZ  RAMOS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>01-10-2026 9:30:16</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>599</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>30-03-2027 9:30:16</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>112241</v>
+      </c>
+      <c r="C14" t="n">
+        <v>154646</v>
+      </c>
+      <c r="D14" t="n">
+        <v>52201</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DAVID EMILIANO  MALDONADO  VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>01-10-2026 9:34:09</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>599</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>30-03-2027 9:34:09</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>111012</v>
+      </c>
+      <c r="C15" t="n">
+        <v>68471</v>
+      </c>
+      <c r="D15" t="n">
+        <v>66299</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>JESUS MAURICIO VALTIERRA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>15-09-2026 19:54:08</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>499</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>10-09-2027 19:54:08</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>102987</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>110818</v>
+      </c>
+      <c r="C16" t="n">
+        <v>312013</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>09512</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>JESUS GUSTAVO MARQUEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>14-09-2026 15:17:57</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>499</v>
+      </c>
+      <c r="M16" t="n">
+        <v>11</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>09-09-2027 15:17:57</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>76787</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>112237</v>
+      </c>
+      <c r="C17" t="n">
+        <v>387278</v>
+      </c>
+      <c r="D17" t="n">
+        <v>29435</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ANA ABIGAIL GUILLEN ENRIQUEZ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>01-10-2026 7:46:21</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>549</v>
+      </c>
+      <c r="M17" t="n">
+        <v>11</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>26-09-2027 7:46:21</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>112187</v>
+      </c>
+      <c r="C18" t="n">
+        <v>164685</v>
+      </c>
+      <c r="D18" t="n">
+        <v>62218</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OSCAR EDCARDA GUZMAN GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>30-09-2026 15:16:45</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>549</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>102910</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>110106</v>
+      </c>
+      <c r="C19" t="n">
+        <v>204657</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>02165</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ERANDI LIZBETH CRUZ  CASTILLO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>02-09-2026 13:25:36</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>399</v>
+      </c>
+      <c r="M19" t="n">
+        <v>11</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>28-08-2027 13:25:36</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>7977</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>112253</v>
+      </c>
+      <c r="C20" t="n">
+        <v>387797</v>
+      </c>
+      <c r="D20" t="n">
+        <v>29954</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>JOSHA JANDRY  BELLO  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>01-10-2026 13:06:16</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>649</v>
+      </c>
+      <c r="M20" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>26-09-2027 13:06:16</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>112234</v>
+      </c>
+      <c r="C21" t="n">
+        <v>386565</v>
+      </c>
+      <c r="D21" t="n">
+        <v>28722</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>JOSE ARMANDO BARAJAS GONGORA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>01-10-2026 6:16:40</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>949</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>112235</v>
+      </c>
+      <c r="C22" t="n">
+        <v>387285</v>
+      </c>
+      <c r="D22" t="n">
+        <v>29442</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CAMILA CERRILLO ESTRADA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>01-10-2026 7:29:03</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>949</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>112249</v>
+      </c>
+      <c r="C23" t="n">
+        <v>387788</v>
+      </c>
+      <c r="D23" t="n">
+        <v>29945</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA PIGNI RIMOLDI</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>01-10-2026 11:52:36</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>799</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>112252</v>
+      </c>
+      <c r="C24" t="n">
+        <v>200980</v>
+      </c>
+      <c r="D24" t="n">
+        <v>98487</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>JOSE ARTURO HURTADO ESQUER</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>01-10-2026 12:52:41</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>699</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>30-03-2027 12:52:41</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>10528</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>112247</v>
+      </c>
+      <c r="C25" t="n">
+        <v>387785</v>
+      </c>
+      <c r="D25" t="n">
+        <v>29942</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GERARDO GONZALEZ REBOLLOSO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>01-10-2026 11:33:27</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>949</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Reporte generado: 01-10-2026 08:18 p. m.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,32 +603,32 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>112239</v>
+        <v>112309</v>
       </c>
       <c r="C3" t="n">
-        <v>387765</v>
+        <v>383098</v>
       </c>
       <c r="D3" t="n">
-        <v>29922</v>
+        <v>25255</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GABRIELA NICOLE INZUNZA VILLARREAL</t>
+          <t>BRENDA TAPIA CHAVEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>01-10-2026 9:06:03</t>
+          <t>02-10-2026 8:09:50</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -645,19 +645,17 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>999</v>
-      </c>
-      <c r="M3" t="n">
-        <v>11</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>26-09-2027 9:06:03</t>
-        </is>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -668,32 +666,32 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>110100</v>
+        <v>112311</v>
       </c>
       <c r="C4" t="n">
-        <v>289981</v>
+        <v>387546</v>
       </c>
       <c r="D4" t="n">
-        <v>87479</v>
+        <v>29703</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RICARDO HERNANDEZ CASTILLO</t>
+          <t>LUIS FRANCISCO ORTEGA FRANCO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02-09-2026 10:19:32</t>
+          <t>02-10-2026 9:43:43</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -706,18 +704,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>499</v>
+        <v>599</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>28-08-2027 10:19:32</t>
+          <t>31-03-2027 9:43:43</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -725,9 +723,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>107633</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -735,27 +731,27 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>111587</v>
+        <v>112269</v>
       </c>
       <c r="C5" t="n">
-        <v>339078</v>
+        <v>387844</v>
       </c>
       <c r="D5" t="n">
-        <v>16896</v>
+        <v>30001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PEDRO  MORALEZ  ESPARZA</t>
+          <t>DANIELA MONTSERRAT MARTINEZ  PLASCENCIA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-09-2026 18:35:31</t>
+          <t>01-10-2026 16:54:08</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -773,18 +769,18 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>649</v>
+        <v>599</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>17-09-2027 18:35:31</t>
+          <t>30-03-2027 16:54:08</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -792,9 +788,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>91215</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -802,32 +796,32 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>112232</v>
+        <v>111736</v>
       </c>
       <c r="C6" t="n">
-        <v>262903</v>
+        <v>382132</v>
       </c>
       <c r="D6" t="n">
-        <v>60407</v>
+        <v>24289</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAUL  ZUÑIGA MARTINEZ</t>
+          <t>DAFNE VALERIA SARABIA  ALTAMIRANO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>01-10-2026 5:44:16</t>
+          <t>24-09-2026 15:01:07</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>30-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -840,11 +834,11 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>549</v>
+        <v>599</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -857,7 +851,9 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>109992</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -865,27 +861,27 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>112246</v>
+        <v>112272</v>
       </c>
       <c r="C7" t="n">
-        <v>386941</v>
+        <v>387850</v>
       </c>
       <c r="D7" t="n">
-        <v>29098</v>
+        <v>30007</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FABIOLA  PLAZA  CARMONA</t>
+          <t>PAMINGER FLORIAN  FLORIAN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01-10-2026 11:04:12</t>
+          <t>01-10-2026 16:59:14</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -907,19 +903,17 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>849</v>
-      </c>
-      <c r="M7" t="n">
-        <v>11</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>26-09-2027 11:04:12</t>
-        </is>
-      </c>
+        <v>799</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -930,27 +924,27 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112243</v>
+        <v>110227</v>
       </c>
       <c r="C8" t="n">
-        <v>118726</v>
+        <v>382358</v>
       </c>
       <c r="D8" t="n">
-        <v>16436</v>
+        <v>24515</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JONATHAN BERNAL REYNA</t>
+          <t>MARISOL  ACUÑA VAZQUEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>STA CATARINA</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>01-10-2026 9:47:38</t>
+          <t>03-09-2026 21:18:41</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -968,26 +962,26 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>599</v>
-      </c>
-      <c r="M8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>30-03-2027 9:47:38</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>110080</v>
+      </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -995,27 +989,27 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>110227</v>
+        <v>112290</v>
       </c>
       <c r="C9" t="n">
-        <v>382358</v>
+        <v>387881</v>
       </c>
       <c r="D9" t="n">
-        <v>24515</v>
+        <v>30038</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MARISOL  ACUÑA VAZQUEZ</t>
+          <t>ALFREDO QUEZADA CURIEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>03-09-2026 21:18:41</t>
+          <t>01-10-2026 18:44:30</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1033,26 +1027,26 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>649</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>999</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>26-09-2027 18:44:30</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>110080</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1060,32 +1054,32 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>112244</v>
+        <v>112307</v>
       </c>
       <c r="C10" t="n">
-        <v>157095</v>
+        <v>387513</v>
       </c>
       <c r="D10" t="n">
-        <v>54639</v>
+        <v>29670</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MARIA DE LOURDES ALVARES PADILLA</t>
+          <t>LIZETH RAMIREZ MARTINEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>01-10-2026 10:15:02</t>
+          <t>02-10-2026 7:13:03</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30-10-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1098,18 +1092,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>399</v>
+        <v>649</v>
       </c>
       <c r="M10" t="n">
         <v>11</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>26-09-2027 10:15:02</t>
+          <t>27-09-2027 7:13:03</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1117,9 +1111,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>4233</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1127,32 +1119,32 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>112251</v>
+        <v>112244</v>
       </c>
       <c r="C11" t="n">
-        <v>387791</v>
+        <v>157095</v>
       </c>
       <c r="D11" t="n">
-        <v>29948</v>
+        <v>54639</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ANGEL GABRIEL RIVERA SALAZAR</t>
+          <t>MARIA DE LOURDES ALVARES PADILLA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01-10-2026 12:36:00</t>
+          <t>01-10-2026 10:15:02</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>30-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1165,18 +1157,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>849</v>
+        <v>399</v>
       </c>
       <c r="M11" t="n">
         <v>11</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>26-09-2027 12:36:00</t>
+          <t>26-09-2027 10:15:02</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1184,7 +1176,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>4233</v>
+      </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1192,27 +1186,27 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>112248</v>
+        <v>112251</v>
       </c>
       <c r="C12" t="n">
-        <v>67098</v>
+        <v>387791</v>
       </c>
       <c r="D12" t="n">
-        <v>64929</v>
+        <v>29948</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JARI BLANCARTE CASTRO</t>
+          <t>ANGEL GABRIEL RIVERA SALAZAR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>01-10-2026 11:45:13</t>
+          <t>01-10-2026 12:36:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1234,14 +1228,14 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>599</v>
+        <v>849</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>30-03-2027 11:45:13</t>
+          <t>26-09-2027 12:36:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1257,32 +1251,32 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>112240</v>
+        <v>112319</v>
       </c>
       <c r="C13" t="n">
-        <v>326427</v>
+        <v>387974</v>
       </c>
       <c r="D13" t="n">
-        <v>23366</v>
+        <v>30131</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ANABEL GÓMEZ  RAMOS</t>
+          <t>UZIEL PICON  SOLIS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>STA CATARINA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>01-10-2026 9:30:16</t>
+          <t>02-10-2026 11:58:57</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-01-2027 23:59:59</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1299,14 +1293,14 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>599</v>
+        <v>1549</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>30-03-2027 9:30:16</t>
+          <t>27-09-2027 11:58:57</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1322,27 +1316,29 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>112241</v>
+        <v>112274</v>
       </c>
       <c r="C14" t="n">
-        <v>154646</v>
-      </c>
-      <c r="D14" t="n">
-        <v>52201</v>
+        <v>111039</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>08776</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DAVID EMILIANO  MALDONADO  VELASQUEZ</t>
+          <t>PEDRO MARIO  VALENZUELA  PINTO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>AZAHARES CUL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01-10-2026 9:34:09</t>
+          <t>01-10-2026 17:03:49</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1364,19 +1360,17 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>599</v>
-      </c>
-      <c r="M14" t="n">
-        <v>5</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>30-03-2027 9:34:09</t>
-        </is>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1387,27 +1381,27 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>111012</v>
+        <v>112281</v>
       </c>
       <c r="C15" t="n">
-        <v>68471</v>
+        <v>381005</v>
       </c>
       <c r="D15" t="n">
-        <v>66299</v>
+        <v>23163</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JESUS MAURICIO VALTIERRA HERNANDEZ</t>
+          <t>RICARDO ALFREDO ARANDA DOWLING</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>15-09-2026 19:54:08</t>
+          <t>01-10-2026 18:07:45</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1425,28 +1419,24 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>499</v>
-      </c>
-      <c r="M15" t="n">
-        <v>11</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>10-09-2027 19:54:08</t>
-        </is>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>102987</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1454,29 +1444,27 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>110818</v>
+        <v>108953</v>
       </c>
       <c r="C16" t="n">
-        <v>312013</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>09512</t>
-        </is>
+        <v>379812</v>
+      </c>
+      <c r="D16" t="n">
+        <v>21970</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JESUS GUSTAVO MARQUEZ GONZALEZ</t>
+          <t>VICTOR  CORTINAS  FAVELA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14-09-2026 15:17:57</t>
+          <t>18-08-2026 17:37:56</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1494,18 +1482,18 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>499</v>
+        <v>849</v>
       </c>
       <c r="M16" t="n">
         <v>11</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>09-09-2027 15:17:57</t>
+          <t>13-08-2027 17:37:56</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1513,9 +1501,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P16" t="n">
-        <v>76787</v>
-      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1523,27 +1509,27 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>112237</v>
+        <v>112243</v>
       </c>
       <c r="C17" t="n">
-        <v>387278</v>
+        <v>118726</v>
       </c>
       <c r="D17" t="n">
-        <v>29435</v>
+        <v>16436</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ANA ABIGAIL GUILLEN ENRIQUEZ</t>
+          <t>JONATHAN BERNAL REYNA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>01-10-2026 7:46:21</t>
+          <t>01-10-2026 9:47:38</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1565,14 +1551,14 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>549</v>
+        <v>599</v>
       </c>
       <c r="M17" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>26-09-2027 7:46:21</t>
+          <t>30-03-2027 9:47:38</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1588,27 +1574,27 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>112187</v>
+        <v>112276</v>
       </c>
       <c r="C18" t="n">
-        <v>164685</v>
+        <v>90016</v>
       </c>
       <c r="D18" t="n">
-        <v>62218</v>
+        <v>87793</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OSCAR EDCARDA GUZMAN GONZALEZ</t>
+          <t>FRANCISCO GONZALEZ CHARLES</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>30-09-2026 15:16:45</t>
+          <t>01-10-2026 17:27:02</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1626,26 +1612,26 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>549</v>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>26-09-2027 17:27:02</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>102910</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1653,29 +1639,27 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>110106</v>
+        <v>112261</v>
       </c>
       <c r="C19" t="n">
-        <v>204657</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>02165</t>
-        </is>
+        <v>387404</v>
+      </c>
+      <c r="D19" t="n">
+        <v>29561</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ERANDI LIZBETH CRUZ  CASTILLO</t>
+          <t>CELENE VILLANUEVA  BRIONES</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>02-09-2026 13:25:36</t>
+          <t>01-10-2026 14:57:54</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1693,28 +1677,24 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>399</v>
-      </c>
-      <c r="M19" t="n">
-        <v>11</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>28-08-2027 13:25:36</t>
-        </is>
-      </c>
+        <v>949</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>7977</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1722,27 +1702,27 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>112253</v>
+        <v>112295</v>
       </c>
       <c r="C20" t="n">
-        <v>387797</v>
+        <v>347831</v>
       </c>
       <c r="D20" t="n">
-        <v>29954</v>
+        <v>89996</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JOSHA JANDRY  BELLO  GONZALEZ</t>
+          <t>CARLOS ALBERTO LOPEZ ALARCON</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01-10-2026 13:06:16</t>
+          <t>01-10-2026 19:21:26</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1760,18 +1740,18 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>649</v>
+        <v>699</v>
       </c>
       <c r="M20" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>26-09-2027 13:06:16</t>
+          <t>30-03-2027 19:21:26</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1779,7 +1759,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>95613</v>
+      </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1787,27 +1769,27 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>112234</v>
+        <v>110100</v>
       </c>
       <c r="C21" t="n">
-        <v>386565</v>
+        <v>289981</v>
       </c>
       <c r="D21" t="n">
-        <v>28722</v>
+        <v>87479</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>JOSE ARMANDO BARAJAS GONGORA</t>
+          <t>RICARDO HERNANDEZ CASTILLO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>01-10-2026 6:16:40</t>
+          <t>02-09-2026 10:19:32</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1825,24 +1807,28 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>949</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M21" t="n">
+        <v>11</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>28-08-2027 10:19:32</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>107633</v>
+      </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1850,27 +1836,27 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>112235</v>
+        <v>111587</v>
       </c>
       <c r="C22" t="n">
-        <v>387285</v>
+        <v>339078</v>
       </c>
       <c r="D22" t="n">
-        <v>29442</v>
+        <v>16896</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CAMILA CERRILLO ESTRADA</t>
+          <t>PEDRO  MORALEZ  ESPARZA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>01-10-2026 7:29:03</t>
+          <t>22-09-2026 18:35:31</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1888,24 +1874,28 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>949</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+        <v>649</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>17-09-2027 18:35:31</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>91215</v>
+      </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1913,27 +1903,29 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>112249</v>
+        <v>112289</v>
       </c>
       <c r="C23" t="n">
-        <v>387788</v>
-      </c>
-      <c r="D23" t="n">
-        <v>29945</v>
+        <v>9780</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>08709</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA PIGNI RIMOLDI</t>
+          <t>CONSUELO MUÑOZ ROSALES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>01-10-2026 11:52:36</t>
+          <t>01-10-2026 18:43:56</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1955,17 +1947,19 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>799</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+        <v>999</v>
+      </c>
+      <c r="M23" t="n">
+        <v>11</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>26-09-2027 18:43:56</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -1976,27 +1970,27 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>112252</v>
+        <v>112232</v>
       </c>
       <c r="C24" t="n">
-        <v>200980</v>
+        <v>262903</v>
       </c>
       <c r="D24" t="n">
-        <v>98487</v>
+        <v>60407</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JOSE ARTURO HURTADO ESQUER</t>
+          <t>RAUL  ZUÑIGA MARTINEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>01-10-2026 12:52:41</t>
+          <t>01-10-2026 5:44:16</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2014,28 +2008,24 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>699</v>
-      </c>
-      <c r="M24" t="n">
-        <v>5</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>30-03-2027 12:52:41</t>
-        </is>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>10528</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2043,17 +2033,17 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>112247</v>
+        <v>112246</v>
       </c>
       <c r="C25" t="n">
-        <v>387785</v>
+        <v>386941</v>
       </c>
       <c r="D25" t="n">
-        <v>29942</v>
+        <v>29098</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GERARDO GONZALEZ REBOLLOSO</t>
+          <t>FABIOLA  PLAZA  CARMONA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2063,7 +2053,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>01-10-2026 11:33:27</t>
+          <t>01-10-2026 11:04:12</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2085,44 +2075,3946 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>949</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+        <v>849</v>
+      </c>
+      <c r="M25" t="n">
+        <v>11</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>26-09-2027 11:04:12</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Reporte generado: 01-10-2026 08:18 p. m.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>112296</v>
+      </c>
+      <c r="C26" t="n">
+        <v>387909</v>
+      </c>
+      <c r="D26" t="n">
+        <v>30066</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CESAR JOSUE  ROJO  OSORIO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>01-10-2026 19:22:26</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>699</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>112239</v>
+      </c>
+      <c r="C27" t="n">
+        <v>387765</v>
+      </c>
+      <c r="D27" t="n">
+        <v>29922</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GABRIELA NICOLE INZUNZA VILLARREAL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>01-10-2026 9:06:03</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>11</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>26-09-2027 9:06:03</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>112256</v>
+      </c>
+      <c r="C28" t="n">
+        <v>106839</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>04582</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>JAVIER SAUCEDO GUERRERO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>01-10-2026 13:31:57</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>699</v>
+      </c>
+      <c r="M28" t="n">
+        <v>5</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>30-03-2027 13:31:57</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>82349</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>112288</v>
+      </c>
+      <c r="C29" t="n">
+        <v>387884</v>
+      </c>
+      <c r="D29" t="n">
+        <v>30041</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DULCE MARIA  SERRANO  JUAREZ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>01-10-2026 18:41:11</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>699</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>30-03-2027 18:41:11</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>112305</v>
+      </c>
+      <c r="C30" t="n">
+        <v>211527</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>09035</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ALAN GEOVANNI RAMOS  FLORES</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>02-10-2026 6:28:46</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>599</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>31-03-2027 6:28:46</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>112303</v>
+      </c>
+      <c r="C31" t="n">
+        <v>222817</v>
+      </c>
+      <c r="D31" t="n">
+        <v>20324</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>FRANCISCO  ROCHA LOPEZ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>02-10-2026 5:28:54</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>699</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>112317</v>
+      </c>
+      <c r="C32" t="n">
+        <v>362544</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>04704</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>DARIO ABRAM  GARCIA  REYNADA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>02-10-2026 11:20:56</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>16-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>649</v>
+      </c>
+      <c r="M32" t="n">
+        <v>11</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>27-09-2027 11:20:56</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>101529</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>112265</v>
+      </c>
+      <c r="C33" t="n">
+        <v>387835</v>
+      </c>
+      <c r="D33" t="n">
+        <v>29992</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VICTOR MARCELO CORTINAS FLORES</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>01-10-2026 16:15:24</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>849</v>
+      </c>
+      <c r="M33" t="n">
+        <v>11</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>26-09-2027 16:15:24</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>112312</v>
+      </c>
+      <c r="C34" t="n">
+        <v>156642</v>
+      </c>
+      <c r="D34" t="n">
+        <v>54186</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MARIA DEL ROCIO  RODRIGUEZ  FELIX</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>02-10-2026 10:15:11</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>699</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>112241</v>
+      </c>
+      <c r="C35" t="n">
+        <v>154646</v>
+      </c>
+      <c r="D35" t="n">
+        <v>52201</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DAVID EMILIANO  MALDONADO  VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>01-10-2026 9:34:09</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>599</v>
+      </c>
+      <c r="M35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>30-03-2027 9:34:09</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>112286</v>
+      </c>
+      <c r="C36" t="n">
+        <v>387878</v>
+      </c>
+      <c r="D36" t="n">
+        <v>30035</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BRYAN ISRAEL GARCIA  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>01-10-2026 18:28:15</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>549</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>112108</v>
+      </c>
+      <c r="C37" t="n">
+        <v>171319</v>
+      </c>
+      <c r="D37" t="n">
+        <v>68838</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>MARIA  DE JESUS CARDONA ALVARADO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>29-09-2026 18:05:34</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>449</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>28-03-2027 18:05:34</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>77276</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>112240</v>
+      </c>
+      <c r="C38" t="n">
+        <v>326427</v>
+      </c>
+      <c r="D38" t="n">
+        <v>23366</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ANABEL GÓMEZ  RAMOS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>01-10-2026 9:30:16</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>599</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>30-03-2027 9:30:16</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>112257</v>
+      </c>
+      <c r="C39" t="n">
+        <v>5992</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>04930</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>JAZMIN GUADALUPE ARELLANOS SAUCEDA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>01-10-2026 13:46:44</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>599</v>
+      </c>
+      <c r="M39" t="n">
+        <v>5</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>30-03-2027 13:46:44</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>112287</v>
+      </c>
+      <c r="C40" t="n">
+        <v>330617</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15671</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAMIRO MARTINEZ RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>01-10-2026 18:35:12</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>549</v>
+      </c>
+      <c r="M40" t="n">
+        <v>11</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>26-09-2027 18:35:12</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>112271</v>
+      </c>
+      <c r="C41" t="n">
+        <v>387846</v>
+      </c>
+      <c r="D41" t="n">
+        <v>30003</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MARIA CRISTINA GARCIA GOMEZ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>01-10-2026 16:57:21</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>949</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>112267</v>
+      </c>
+      <c r="C42" t="n">
+        <v>339819</v>
+      </c>
+      <c r="D42" t="n">
+        <v>17637</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>TOBIAS FREIDTAINS FREIDTAINS</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>01-10-2026 16:52:34</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>799</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>112315</v>
+      </c>
+      <c r="C43" t="n">
+        <v>387966</v>
+      </c>
+      <c r="D43" t="n">
+        <v>30123</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>MAURICIO MACIAS SILLER</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>02-10-2026 10:56:58</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>949</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>111012</v>
+      </c>
+      <c r="C44" t="n">
+        <v>68471</v>
+      </c>
+      <c r="D44" t="n">
+        <v>66299</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>JESUS MAURICIO VALTIERRA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>15-09-2026 19:54:08</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>499</v>
+      </c>
+      <c r="M44" t="n">
+        <v>11</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>10-09-2027 19:54:08</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>102987</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>110103</v>
+      </c>
+      <c r="C45" t="n">
+        <v>202835</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>00343</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CRISTOBAL TIRADO CASTAÑEDA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>02-09-2026 11:12:05</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>499</v>
+      </c>
+      <c r="M45" t="n">
+        <v>11</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>28-08-2027 11:12:05</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>91359</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>110104</v>
+      </c>
+      <c r="C46" t="n">
+        <v>129528</v>
+      </c>
+      <c r="D46" t="n">
+        <v>27196</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>MARCO ANTONIO BARRAZA  PAREDES</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>02-09-2026 11:17:33</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>399</v>
+      </c>
+      <c r="M46" t="n">
+        <v>11</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>28-08-2027 11:17:33</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>66241</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>112258</v>
+      </c>
+      <c r="C47" t="n">
+        <v>350328</v>
+      </c>
+      <c r="D47" t="n">
+        <v>92492</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PAMELA RODRIGUEZ N</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>01-10-2026 14:03:38</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>649</v>
+      </c>
+      <c r="M47" t="n">
+        <v>11</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>26-09-2027 14:03:38</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>112294</v>
+      </c>
+      <c r="C48" t="n">
+        <v>387904</v>
+      </c>
+      <c r="D48" t="n">
+        <v>30061</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LAISHA AMAIRAMI DOMINGUEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>01-10-2026 19:16:44</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>699</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>112270</v>
+      </c>
+      <c r="C49" t="n">
+        <v>385596</v>
+      </c>
+      <c r="D49" t="n">
+        <v>27753</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LUIS GIOVANNIE GARCIA  HERNADEZ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>01-10-2026 16:55:45</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>01-01-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M49" t="n">
+        <v>9</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>26-09-2027 16:55:45</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>112293</v>
+      </c>
+      <c r="C50" t="n">
+        <v>134981</v>
+      </c>
+      <c r="D50" t="n">
+        <v>32629</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA  RAMON  DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>01-10-2026 19:11:32</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>599</v>
+      </c>
+      <c r="M50" t="n">
+        <v>5</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>30-03-2027 19:11:32</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>112302</v>
+      </c>
+      <c r="C51" t="n">
+        <v>351343</v>
+      </c>
+      <c r="D51" t="n">
+        <v>93507</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ASTRID ESTHEFANY ORGEN  OBESO</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>01-10-2026 20:10:26</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>599</v>
+      </c>
+      <c r="M51" t="n">
+        <v>5</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>30-03-2027 20:10:26</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>112238</v>
+      </c>
+      <c r="C52" t="n">
+        <v>36177</v>
+      </c>
+      <c r="D52" t="n">
+        <v>34091</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DENISSE  VARGAS MARTINEZZ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>01-10-2026 8:10:41</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>599</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>53295</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>112304</v>
+      </c>
+      <c r="C53" t="n">
+        <v>387933</v>
+      </c>
+      <c r="D53" t="n">
+        <v>30090</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ALISON ORTEGA GOMEZ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>02-10-2026 6:15:03</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>549</v>
+      </c>
+      <c r="M53" t="n">
+        <v>11</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>27-09-2027 6:15:03</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>112253</v>
+      </c>
+      <c r="C54" t="n">
+        <v>387797</v>
+      </c>
+      <c r="D54" t="n">
+        <v>29954</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>JOSHA JANDRY  BELLO  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>01-10-2026 13:06:16</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>649</v>
+      </c>
+      <c r="M54" t="n">
+        <v>11</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>26-09-2027 13:06:16</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>112292</v>
+      </c>
+      <c r="C55" t="n">
+        <v>386711</v>
+      </c>
+      <c r="D55" t="n">
+        <v>28868</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ANA DELIA  LOPEZ  NIEBLAS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>01-10-2026 19:10:21</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>599</v>
+      </c>
+      <c r="M55" t="n">
+        <v>5</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>30-03-2027 19:10:21</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>112310</v>
+      </c>
+      <c r="C56" t="n">
+        <v>387950</v>
+      </c>
+      <c r="D56" t="n">
+        <v>30107</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>GABRIEL TREJO CAMACHO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>02-10-2026 8:42:40</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>849</v>
+      </c>
+      <c r="M56" t="n">
+        <v>11</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>27-09-2027 8:42:40</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>112280</v>
+      </c>
+      <c r="C57" t="n">
+        <v>125817</v>
+      </c>
+      <c r="D57" t="n">
+        <v>23492</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ALEJANDRO  ARREDONDO BOJORQUEZ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>01-10-2026 18:03:34</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>699</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>43718</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>112300</v>
+      </c>
+      <c r="C58" t="n">
+        <v>387867</v>
+      </c>
+      <c r="D58" t="n">
+        <v>30024</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>GUADALUPE GEORGINA  GONZALEZ CIRIGO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>01-10-2026 19:36:27</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>649</v>
+      </c>
+      <c r="M58" t="n">
+        <v>11</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>26-09-2027 19:36:27</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>112187</v>
+      </c>
+      <c r="C59" t="n">
+        <v>164685</v>
+      </c>
+      <c r="D59" t="n">
+        <v>62218</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>OSCAR EDCARDA GUZMAN GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>30-09-2026 15:16:45</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>549</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>102910</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>110106</v>
+      </c>
+      <c r="C60" t="n">
+        <v>204657</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>02165</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ERANDI LIZBETH CRUZ  CASTILLO</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>02-09-2026 13:25:36</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>399</v>
+      </c>
+      <c r="M60" t="n">
+        <v>11</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>28-08-2027 13:25:36</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>7977</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>112263</v>
+      </c>
+      <c r="C61" t="n">
+        <v>387820</v>
+      </c>
+      <c r="D61" t="n">
+        <v>29977</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RICARDO RAMIREZ  MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>01-10-2026 15:26:38</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>599</v>
+      </c>
+      <c r="M61" t="n">
+        <v>5</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>30-03-2027 15:26:38</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>112299</v>
+      </c>
+      <c r="C62" t="n">
+        <v>387908</v>
+      </c>
+      <c r="D62" t="n">
+        <v>30065</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ERIKA NATCHA MARTINEZ ANTONIO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>01-10-2026 19:28:17</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>599</v>
+      </c>
+      <c r="M62" t="n">
+        <v>5</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>30-03-2027 19:28:17</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>112237</v>
+      </c>
+      <c r="C63" t="n">
+        <v>387278</v>
+      </c>
+      <c r="D63" t="n">
+        <v>29435</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ANA ABIGAIL GUILLEN ENRIQUEZ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>01-10-2026 7:46:21</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>549</v>
+      </c>
+      <c r="M63" t="n">
+        <v>11</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>26-09-2027 7:46:21</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>112322</v>
+      </c>
+      <c r="C64" t="n">
+        <v>387986</v>
+      </c>
+      <c r="D64" t="n">
+        <v>30143</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>MANUELA DE JESUS RUIZ ALUCANO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>02-10-2026 13:00:38</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>549</v>
+      </c>
+      <c r="M64" t="n">
+        <v>11</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>27-09-2027 13:00:38</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>110818</v>
+      </c>
+      <c r="C65" t="n">
+        <v>312013</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>09512</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>JESUS GUSTAVO MARQUEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>14-09-2026 15:17:57</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>499</v>
+      </c>
+      <c r="M65" t="n">
+        <v>11</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>09-09-2027 15:17:57</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>76787</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>112278</v>
+      </c>
+      <c r="C66" t="n">
+        <v>387863</v>
+      </c>
+      <c r="D66" t="n">
+        <v>30020</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>FERNANDO  MANRIQUE MELLADO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>01-10-2026 17:43:45</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>549</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>112298</v>
+      </c>
+      <c r="C67" t="n">
+        <v>387453</v>
+      </c>
+      <c r="D67" t="n">
+        <v>29610</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>MARCELA GOMEZ DEANDAR</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>01-10-2026 19:27:30</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>849</v>
+      </c>
+      <c r="M67" t="n">
+        <v>11</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>26-09-2027 19:27:30</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>112268</v>
+      </c>
+      <c r="C68" t="n">
+        <v>387603</v>
+      </c>
+      <c r="D68" t="n">
+        <v>29760</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ALEXIS TERRAZA VALENZUELA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>01-10-2026 16:52:36</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>599</v>
+      </c>
+      <c r="M68" t="n">
+        <v>5</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>30-03-2027 16:52:36</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>112273</v>
+      </c>
+      <c r="C69" t="n">
+        <v>387843</v>
+      </c>
+      <c r="D69" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>GUADALUPE JAVIER CHAPA  HERRERA</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>01-10-2026 17:02:04</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>949</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>112248</v>
+      </c>
+      <c r="C70" t="n">
+        <v>67098</v>
+      </c>
+      <c r="D70" t="n">
+        <v>64929</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>JARI BLANCARTE CASTRO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>01-10-2026 11:45:13</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>CANCELADO</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>599</v>
+      </c>
+      <c r="M70" t="n">
+        <v>5</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>30-03-2027 11:45:13</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>112279</v>
+      </c>
+      <c r="C71" t="n">
+        <v>277374</v>
+      </c>
+      <c r="D71" t="n">
+        <v>74875</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>MARIA ISABEL SOJO REYNAGA</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>01-10-2026 17:59:41</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>04-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>549</v>
+      </c>
+      <c r="M71" t="n">
+        <v>11</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>26-09-2027 17:59:41</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>112252</v>
+      </c>
+      <c r="C72" t="n">
+        <v>200980</v>
+      </c>
+      <c r="D72" t="n">
+        <v>98487</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>JOSE ARTURO HURTADO ESQUER</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>01-10-2026 12:52:41</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>699</v>
+      </c>
+      <c r="M72" t="n">
+        <v>5</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>30-03-2027 12:52:41</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>10528</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>112277</v>
+      </c>
+      <c r="C73" t="n">
+        <v>387864</v>
+      </c>
+      <c r="D73" t="n">
+        <v>30021</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>JESUS JULIAN GALLEGOS HERREEA</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>01-10-2026 17:42:25</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>549</v>
+      </c>
+      <c r="M73" t="n">
+        <v>11</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>26-09-2027 17:42:25</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>112284</v>
+      </c>
+      <c r="C74" t="n">
+        <v>387872</v>
+      </c>
+      <c r="D74" t="n">
+        <v>30029</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>MONSERRAT  SAVAAVEDRA  ROJAS</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>01-10-2026 18:20:28</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>549</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>112318</v>
+      </c>
+      <c r="C75" t="n">
+        <v>387972</v>
+      </c>
+      <c r="D75" t="n">
+        <v>30129</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>NANCY  REMIGIO ARZATE</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>02-10-2026 11:31:57</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>699</v>
+      </c>
+      <c r="M75" t="n">
+        <v>5</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>31-03-2027 11:31:57</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>112301</v>
+      </c>
+      <c r="C76" t="n">
+        <v>157985</v>
+      </c>
+      <c r="D76" t="n">
+        <v>55528</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>JOHANA JAQUELINE RAMOS ELIZALDE</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>01-10-2026 20:07:43</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>699</v>
+      </c>
+      <c r="M76" t="n">
+        <v>5</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>30-03-2027 20:07:43</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>68615</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>112234</v>
+      </c>
+      <c r="C77" t="n">
+        <v>386565</v>
+      </c>
+      <c r="D77" t="n">
+        <v>28722</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>JOSE ARMANDO BARAJAS GONGORA</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>01-10-2026 6:16:40</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>949</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>110534</v>
+      </c>
+      <c r="C78" t="n">
+        <v>376238</v>
+      </c>
+      <c r="D78" t="n">
+        <v>18398</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RUBEN ALBERTO  GUIZAR  CAMACHO</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>08-09-2026 20:16:38</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>28-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>599</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>107294</v>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>112249</v>
+      </c>
+      <c r="C79" t="n">
+        <v>387788</v>
+      </c>
+      <c r="D79" t="n">
+        <v>29945</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA PIGNI RIMOLDI</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>01-10-2026 11:52:36</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>799</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>112313</v>
+      </c>
+      <c r="C80" t="n">
+        <v>386133</v>
+      </c>
+      <c r="D80" t="n">
+        <v>28290</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>LAURA LETICIA ESPARZA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>02-10-2026 10:20:26</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>949</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>112235</v>
+      </c>
+      <c r="C81" t="n">
+        <v>387285</v>
+      </c>
+      <c r="D81" t="n">
+        <v>29442</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>CAMILA CERRILLO ESTRADA</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>01-10-2026 7:29:03</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>949</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>112285</v>
+      </c>
+      <c r="C82" t="n">
+        <v>387877</v>
+      </c>
+      <c r="D82" t="n">
+        <v>30034</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>GRACIELA VARGAS OCHOA</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>01-10-2026 18:27:20</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>549</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>112247</v>
+      </c>
+      <c r="C83" t="n">
+        <v>387785</v>
+      </c>
+      <c r="D83" t="n">
+        <v>29942</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>GERARDO GONZALEZ REBOLLOSO</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>01-10-2026 11:33:27</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>949</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>112297</v>
+      </c>
+      <c r="C84" t="n">
+        <v>347840</v>
+      </c>
+      <c r="D84" t="n">
+        <v>90005</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>SANTIAGO LOPEZ MALVAEZ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>01-10-2026 19:25:55</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>599</v>
+      </c>
+      <c r="M84" t="n">
+        <v>5</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>30-03-2027 19:25:55</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>112316</v>
+      </c>
+      <c r="C85" t="n">
+        <v>387965</v>
+      </c>
+      <c r="D85" t="n">
+        <v>30122</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>MARIEL LETICIA  MACIAS  ROMAN</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>02-10-2026 11:00:28</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>699</v>
+      </c>
+      <c r="M85" t="n">
+        <v>5</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>31-03-2027 11:00:28</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Reporte generado: 02-10-2026 08:04 p. m.</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q86"/>
+  <dimension ref="A1:Q131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,32 +603,32 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>112309</v>
+        <v>110250</v>
       </c>
       <c r="C3" t="n">
-        <v>383098</v>
+        <v>347993</v>
       </c>
       <c r="D3" t="n">
-        <v>25255</v>
+        <v>90158</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BRENDA TAPIA CHAVEZ</t>
+          <t>VALERY MARISA HERNANDEZ  CASTILLO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>02-10-2026 8:09:50</t>
+          <t>04-09-2026 16:33:31</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -641,24 +641,28 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L3" t="n">
         <v>549</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>30-08-2027 16:33:31</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>95723</v>
+      </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -666,27 +670,27 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>112311</v>
+        <v>112342</v>
       </c>
       <c r="C4" t="n">
-        <v>387546</v>
+        <v>388034</v>
       </c>
       <c r="D4" t="n">
-        <v>29703</v>
+        <v>30191</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LUIS FRANCISCO ORTEGA FRANCO</t>
+          <t>RICARDO NOE  ZUÑIGA  PALACIOS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02-10-2026 9:43:43</t>
+          <t>02-10-2026 17:49:53</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -708,14 +712,14 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>599</v>
+        <v>649</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>31-03-2027 9:43:43</t>
+          <t>27-09-2027 17:49:53</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -731,27 +735,27 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>112269</v>
+        <v>112281</v>
       </c>
       <c r="C5" t="n">
-        <v>387844</v>
+        <v>381005</v>
       </c>
       <c r="D5" t="n">
-        <v>30001</v>
+        <v>23163</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DANIELA MONTSERRAT MARTINEZ  PLASCENCIA</t>
+          <t>RICARDO ALFREDO ARANDA DOWLING</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01-10-2026 16:54:08</t>
+          <t>01-10-2026 18:07:45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -773,19 +777,17 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>599</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>30-03-2027 16:54:08</t>
-        </is>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -796,32 +798,32 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>111736</v>
+        <v>112363</v>
       </c>
       <c r="C6" t="n">
-        <v>382132</v>
+        <v>344891</v>
       </c>
       <c r="D6" t="n">
-        <v>24289</v>
+        <v>22708</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DAFNE VALERIA SARABIA  ALTAMIRANO</t>
+          <t>DAVID CARLOS GALLARDO CONTRERAS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>24-09-2026 15:01:07</t>
+          <t>03-10-2026 8:50:39</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30-10-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -838,21 +840,23 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>599</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>699</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>01-04-2027 8:50:39</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>109992</v>
+        <v>106911</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
@@ -861,32 +865,32 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>112272</v>
+        <v>112352</v>
       </c>
       <c r="C7" t="n">
-        <v>387850</v>
+        <v>388094</v>
       </c>
       <c r="D7" t="n">
-        <v>30007</v>
+        <v>30251</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PAMINGER FLORIAN  FLORIAN</t>
+          <t>MIRIAM SELENE GARCIA POYORENA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01-10-2026 16:59:14</t>
+          <t>02-10-2026 20:37:21</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -903,17 +907,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>799</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>31-03-2027 20:37:21</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -924,32 +930,32 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110227</v>
+        <v>112368</v>
       </c>
       <c r="C8" t="n">
-        <v>382358</v>
+        <v>387963</v>
       </c>
       <c r="D8" t="n">
-        <v>24515</v>
+        <v>30120</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MARISOL  ACUÑA VAZQUEZ</t>
+          <t>GIOVANNI ANTONIO VAZQUEZ RANGEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>03-09-2026 21:18:41</t>
+          <t>02-10-2026 10:27:39</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -962,11 +968,11 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>649</v>
+        <v>699</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -979,9 +985,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>110080</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -989,32 +993,32 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>112290</v>
+        <v>112244</v>
       </c>
       <c r="C9" t="n">
-        <v>387881</v>
+        <v>157095</v>
       </c>
       <c r="D9" t="n">
-        <v>30038</v>
+        <v>54639</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ALFREDO QUEZADA CURIEL</t>
+          <t>MARIA DE LOURDES ALVARES PADILLA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>01-10-2026 18:44:30</t>
+          <t>01-10-2026 10:15:02</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>30-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1027,18 +1031,18 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>999</v>
+        <v>399</v>
       </c>
       <c r="M9" t="n">
         <v>11</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>26-09-2027 18:44:30</t>
+          <t>26-09-2027 10:15:02</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1046,7 +1050,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>4233</v>
+      </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1054,32 +1060,32 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>112307</v>
+        <v>112251</v>
       </c>
       <c r="C10" t="n">
-        <v>387513</v>
+        <v>387791</v>
       </c>
       <c r="D10" t="n">
-        <v>29670</v>
+        <v>29948</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LIZETH RAMIREZ MARTINEZ</t>
+          <t>ANGEL GABRIEL RIVERA SALAZAR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>02-10-2026 7:13:03</t>
+          <t>01-10-2026 12:36:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1096,14 +1102,14 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>649</v>
+        <v>849</v>
       </c>
       <c r="M10" t="n">
         <v>11</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>27-09-2027 7:13:03</t>
+          <t>26-09-2027 12:36:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1119,32 +1125,32 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>112244</v>
+        <v>112319</v>
       </c>
       <c r="C11" t="n">
-        <v>157095</v>
+        <v>387974</v>
       </c>
       <c r="D11" t="n">
-        <v>54639</v>
+        <v>30131</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MARIA DE LOURDES ALVARES PADILLA</t>
+          <t>UZIEL PICON  SOLIS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01-10-2026 10:15:02</t>
+          <t>02-10-2026 11:58:57</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30-10-2026 23:59:59</t>
+          <t>02-01-2027 23:59:59</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1157,18 +1163,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>399</v>
+        <v>1549</v>
       </c>
       <c r="M11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>26-09-2027 10:15:02</t>
+          <t>27-09-2027 11:58:57</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1176,9 +1182,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>4233</v>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1186,32 +1190,32 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>112251</v>
+        <v>112362</v>
       </c>
       <c r="C12" t="n">
-        <v>387791</v>
+        <v>383624</v>
       </c>
       <c r="D12" t="n">
-        <v>29948</v>
+        <v>25781</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANGEL GABRIEL RIVERA SALAZAR</t>
+          <t>DAYSI GUADALUPE SANTACRUZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>01-10-2026 12:36:00</t>
+          <t>03-10-2026 8:45:37</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1228,14 +1232,14 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>849</v>
+        <v>599</v>
       </c>
       <c r="M12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>26-09-2027 12:36:00</t>
+          <t>01-04-2027 8:45:37</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1251,32 +1255,32 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>112319</v>
+        <v>110251</v>
       </c>
       <c r="C13" t="n">
-        <v>387974</v>
+        <v>347990</v>
       </c>
       <c r="D13" t="n">
-        <v>30131</v>
+        <v>90155</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UZIEL PICON  SOLIS</t>
+          <t>LUIS ARTURO  HERNANDEZ  SALGADO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>02-10-2026 11:58:57</t>
+          <t>04-09-2026 16:36:08</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>02-01-2027 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1289,18 +1293,18 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1549</v>
+        <v>549</v>
       </c>
       <c r="M13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>27-09-2027 11:58:57</t>
+          <t>30-08-2027 16:36:08</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1308,7 +1312,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>95721</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1381,32 +1387,32 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>112281</v>
+        <v>110240</v>
       </c>
       <c r="C15" t="n">
-        <v>381005</v>
+        <v>90728</v>
       </c>
       <c r="D15" t="n">
-        <v>23163</v>
+        <v>88499</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RICARDO ALFREDO ARANDA DOWLING</t>
+          <t>VALERIA V PEREZ VALDEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>PABELLON RTO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>01-10-2026 18:07:45</t>
+          <t>04-09-2026 9:56:12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1419,11 +1425,11 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>699</v>
+        <v>599</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1436,7 +1442,9 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>107840</v>
+      </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1509,27 +1517,29 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>112243</v>
+        <v>110818</v>
       </c>
       <c r="C17" t="n">
-        <v>118726</v>
-      </c>
-      <c r="D17" t="n">
-        <v>16436</v>
+        <v>312013</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>09512</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JONATHAN BERNAL REYNA</t>
+          <t>JESUS GUSTAVO MARQUEZ GONZALEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>STA CATARINA</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>01-10-2026 9:47:38</t>
+          <t>14-09-2026 15:17:57</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1547,18 +1557,18 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>599</v>
+        <v>499</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>30-03-2027 9:47:38</t>
+          <t>09-09-2027 15:17:57</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1566,7 +1576,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>76787</v>
+      </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1574,17 +1586,17 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>112276</v>
+        <v>112237</v>
       </c>
       <c r="C18" t="n">
-        <v>90016</v>
+        <v>387278</v>
       </c>
       <c r="D18" t="n">
-        <v>87793</v>
+        <v>29435</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FRANCISCO GONZALEZ CHARLES</t>
+          <t>ANA ABIGAIL GUILLEN ENRIQUEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1594,7 +1606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01-10-2026 17:27:02</t>
+          <t>01-10-2026 7:46:21</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1623,7 +1635,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>26-09-2027 17:27:02</t>
+          <t>26-09-2027 7:46:21</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1639,32 +1651,32 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>112261</v>
+        <v>112322</v>
       </c>
       <c r="C19" t="n">
-        <v>387404</v>
+        <v>387986</v>
       </c>
       <c r="D19" t="n">
-        <v>29561</v>
+        <v>30143</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CELENE VILLANUEVA  BRIONES</t>
+          <t>MANUELA DE JESUS RUIZ ALUCANO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>01-10-2026 14:57:54</t>
+          <t>02-10-2026 13:00:38</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1681,17 +1693,19 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>949</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M19" t="n">
+        <v>11</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>27-09-2027 13:00:38</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -1702,27 +1716,27 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>112295</v>
+        <v>112278</v>
       </c>
       <c r="C20" t="n">
-        <v>347831</v>
+        <v>387863</v>
       </c>
       <c r="D20" t="n">
-        <v>89996</v>
+        <v>30020</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO LOPEZ ALARCON</t>
+          <t>FERNANDO  MANRIQUE MELLADO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01-10-2026 19:21:26</t>
+          <t>01-10-2026 17:43:45</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1740,28 +1754,24 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>699</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>30-03-2027 19:21:26</t>
-        </is>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>95613</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1769,32 +1779,32 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>110100</v>
+        <v>112335</v>
       </c>
       <c r="C21" t="n">
-        <v>289981</v>
+        <v>388021</v>
       </c>
       <c r="D21" t="n">
-        <v>87479</v>
+        <v>30178</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RICARDO HERNANDEZ CASTILLO</t>
+          <t>ANGELICA MARIA GRANADOS SANCHEZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>02-09-2026 10:19:32</t>
+          <t>02-10-2026 17:22:05</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1807,18 +1817,18 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>499</v>
+        <v>599</v>
       </c>
       <c r="M21" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>28-08-2027 10:19:32</t>
+          <t>31-03-2027 17:22:05</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1826,9 +1836,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P21" t="n">
-        <v>107633</v>
-      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1836,27 +1844,29 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>111587</v>
+        <v>110106</v>
       </c>
       <c r="C22" t="n">
-        <v>339078</v>
-      </c>
-      <c r="D22" t="n">
-        <v>16896</v>
+        <v>204657</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>02165</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PEDRO  MORALEZ  ESPARZA</t>
+          <t>ERANDI LIZBETH CRUZ  CASTILLO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22-09-2026 18:35:31</t>
+          <t>02-09-2026 13:25:36</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1878,14 +1888,14 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>649</v>
+        <v>399</v>
       </c>
       <c r="M22" t="n">
         <v>11</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>17-09-2027 18:35:31</t>
+          <t>28-08-2027 13:25:36</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1894,7 +1904,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>91215</v>
+        <v>7977</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
@@ -1903,29 +1913,27 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>112289</v>
+        <v>112263</v>
       </c>
       <c r="C23" t="n">
-        <v>9780</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>08709</t>
-        </is>
+        <v>387820</v>
+      </c>
+      <c r="D23" t="n">
+        <v>29977</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CONSUELO MUÑOZ ROSALES</t>
+          <t>RICARDO RAMIREZ  MARTINEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>01-10-2026 18:43:56</t>
+          <t>01-10-2026 15:26:38</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1947,14 +1955,14 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>999</v>
+        <v>599</v>
       </c>
       <c r="M23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>26-09-2027 18:43:56</t>
+          <t>30-03-2027 15:26:38</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1970,27 +1978,27 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>112232</v>
+        <v>112299</v>
       </c>
       <c r="C24" t="n">
-        <v>262903</v>
+        <v>387908</v>
       </c>
       <c r="D24" t="n">
-        <v>60407</v>
+        <v>30065</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAUL  ZUÑIGA MARTINEZ</t>
+          <t>ERIKA NATCHA MARTINEZ ANTONIO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>01-10-2026 5:44:16</t>
+          <t>01-10-2026 19:28:17</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2012,17 +2020,19 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>549</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>30-03-2027 19:28:17</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2033,32 +2043,32 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>112246</v>
+        <v>112343</v>
       </c>
       <c r="C25" t="n">
-        <v>386941</v>
+        <v>388038</v>
       </c>
       <c r="D25" t="n">
-        <v>29098</v>
+        <v>30195</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FABIOLA  PLAZA  CARMONA</t>
+          <t>ABRIL  HURTADO  PICHARDO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>01-10-2026 11:04:12</t>
+          <t>02-10-2026 17:52:26</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2075,14 +2085,14 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>849</v>
+        <v>599</v>
       </c>
       <c r="M25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>26-09-2027 11:04:12</t>
+          <t>31-03-2027 17:52:26</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2098,27 +2108,27 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>112296</v>
+        <v>112300</v>
       </c>
       <c r="C26" t="n">
-        <v>387909</v>
+        <v>387867</v>
       </c>
       <c r="D26" t="n">
-        <v>30066</v>
+        <v>30024</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CESAR JOSUE  ROJO  OSORIO</t>
+          <t>GUADALUPE GEORGINA  GONZALEZ CIRIGO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SAN ISIDRO CUL</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>01-10-2026 19:22:26</t>
+          <t>01-10-2026 19:36:27</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2140,17 +2150,19 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>699</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+        <v>649</v>
+      </c>
+      <c r="M26" t="n">
+        <v>11</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>26-09-2027 19:36:27</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2161,32 +2173,32 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>112239</v>
+        <v>112351</v>
       </c>
       <c r="C27" t="n">
-        <v>387765</v>
+        <v>179739</v>
       </c>
       <c r="D27" t="n">
-        <v>29922</v>
+        <v>77246</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GABRIELA NICOLE INZUNZA VILLARREAL</t>
+          <t>MARIA DE LA LUZ MARTINEZ ROMERO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>01-10-2026 9:06:03</t>
+          <t>02-10-2026 19:44:47</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2199,18 +2211,18 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>999</v>
+        <v>699</v>
       </c>
       <c r="M27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>26-09-2027 9:06:03</t>
+          <t>31-03-2027 19:44:47</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2218,7 +2230,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>32522</v>
+      </c>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2226,29 +2240,27 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>112256</v>
+        <v>112187</v>
       </c>
       <c r="C28" t="n">
-        <v>106839</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>04582</t>
-        </is>
+        <v>164685</v>
+      </c>
+      <c r="D28" t="n">
+        <v>62218</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>JAVIER SAUCEDO GUERRERO</t>
+          <t>OSCAR EDCARDA GUZMAN GONZALEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>01-10-2026 13:31:57</t>
+          <t>30-09-2026 15:16:45</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2270,23 +2282,21 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>699</v>
-      </c>
-      <c r="M28" t="n">
-        <v>5</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>30-03-2027 13:31:57</t>
-        </is>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>82349</v>
+        <v>102910</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
@@ -2295,27 +2305,27 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>112288</v>
+        <v>112298</v>
       </c>
       <c r="C29" t="n">
-        <v>387884</v>
+        <v>387453</v>
       </c>
       <c r="D29" t="n">
-        <v>30041</v>
+        <v>29610</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DULCE MARIA  SERRANO  JUAREZ</t>
+          <t>MARCELA GOMEZ DEANDAR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>01-10-2026 18:41:11</t>
+          <t>01-10-2026 19:27:30</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2337,14 +2347,14 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>699</v>
+        <v>849</v>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>30-03-2027 18:41:11</t>
+          <t>26-09-2027 19:27:30</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2360,34 +2370,32 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>112305</v>
+        <v>112239</v>
       </c>
       <c r="C30" t="n">
-        <v>211527</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>09035</t>
-        </is>
+        <v>387765</v>
+      </c>
+      <c r="D30" t="n">
+        <v>29922</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ALAN GEOVANNI RAMOS  FLORES</t>
+          <t>GABRIELA NICOLE INZUNZA VILLARREAL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>02-10-2026 6:28:46</t>
+          <t>01-10-2026 9:06:03</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2404,14 +2412,14 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>599</v>
+        <v>999</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>31-03-2027 6:28:46</t>
+          <t>26-09-2027 9:06:03</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2427,32 +2435,34 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>112303</v>
+        <v>112256</v>
       </c>
       <c r="C31" t="n">
-        <v>222817</v>
-      </c>
-      <c r="D31" t="n">
-        <v>20324</v>
+        <v>106839</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>04582</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FRANCISCO  ROCHA LOPEZ</t>
+          <t>JAVIER SAUCEDO GUERRERO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>02-10-2026 5:28:54</t>
+          <t>01-10-2026 13:31:57</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2465,24 +2475,28 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L31" t="n">
         <v>699</v>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>30-03-2027 13:31:57</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>82349</v>
+      </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2490,19 +2504,17 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>112317</v>
+        <v>112288</v>
       </c>
       <c r="C32" t="n">
-        <v>362544</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>04704</t>
-        </is>
+        <v>387884</v>
+      </c>
+      <c r="D32" t="n">
+        <v>30041</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DARIO ABRAM  GARCIA  REYNADA</t>
+          <t>DULCE MARIA  SERRANO  JUAREZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2512,12 +2524,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>02-10-2026 11:20:56</t>
+          <t>01-10-2026 18:41:11</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>16-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2530,18 +2542,18 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>649</v>
+        <v>699</v>
       </c>
       <c r="M32" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>27-09-2027 11:20:56</t>
+          <t>30-03-2027 18:41:11</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2549,9 +2561,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P32" t="n">
-        <v>101529</v>
-      </c>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2559,32 +2569,34 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>112265</v>
+        <v>112305</v>
       </c>
       <c r="C33" t="n">
-        <v>387835</v>
-      </c>
-      <c r="D33" t="n">
-        <v>29992</v>
+        <v>211527</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>09035</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VICTOR MARCELO CORTINAS FLORES</t>
+          <t>ALAN GEOVANNI RAMOS  FLORES</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>01-10-2026 16:15:24</t>
+          <t>02-10-2026 6:28:46</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2601,14 +2613,14 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>849</v>
+        <v>599</v>
       </c>
       <c r="M33" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>26-09-2027 16:15:24</t>
+          <t>31-03-2027 6:28:46</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2624,27 +2636,27 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>112312</v>
+        <v>112303</v>
       </c>
       <c r="C34" t="n">
-        <v>156642</v>
+        <v>222817</v>
       </c>
       <c r="D34" t="n">
-        <v>54186</v>
+        <v>20324</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MARIA DEL ROCIO  RODRIGUEZ  FELIX</t>
+          <t>FRANCISCO  ROCHA LOPEZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZAHARES CUL</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>02-10-2026 10:15:11</t>
+          <t>02-10-2026 5:28:54</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2687,32 +2699,34 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>112241</v>
+        <v>112317</v>
       </c>
       <c r="C35" t="n">
-        <v>154646</v>
-      </c>
-      <c r="D35" t="n">
-        <v>52201</v>
+        <v>362544</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>04704</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DAVID EMILIANO  MALDONADO  VELASQUEZ</t>
+          <t>DARIO ABRAM  GARCIA  REYNADA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>01-10-2026 9:34:09</t>
+          <t>02-10-2026 11:20:56</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>16-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2725,18 +2739,18 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>599</v>
+        <v>649</v>
       </c>
       <c r="M35" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>30-03-2027 9:34:09</t>
+          <t>27-09-2027 11:20:56</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2744,7 +2758,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>101529</v>
+      </c>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2752,32 +2768,32 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>112286</v>
+        <v>112367</v>
       </c>
       <c r="C36" t="n">
-        <v>387878</v>
+        <v>142180</v>
       </c>
       <c r="D36" t="n">
-        <v>30035</v>
+        <v>39798</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BRYAN ISRAEL GARCIA  GONZALEZ</t>
+          <t>KENIA GUADALUPE SILVA MEDINA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>01-10-2026 18:28:15</t>
+          <t>03-10-2026 10:51:07</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>12-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2790,11 +2806,11 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>549</v>
+        <v>399</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2807,7 +2823,9 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>81999</v>
+      </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2815,32 +2833,32 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>112108</v>
+        <v>112232</v>
       </c>
       <c r="C37" t="n">
-        <v>171319</v>
+        <v>262903</v>
       </c>
       <c r="D37" t="n">
-        <v>68838</v>
+        <v>60407</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MARIA  DE JESUS CARDONA ALVARADO</t>
+          <t>RAUL  ZUÑIGA MARTINEZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>29-09-2026 18:05:34</t>
+          <t>01-10-2026 5:44:16</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2853,28 +2871,24 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>449</v>
-      </c>
-      <c r="M37" t="n">
-        <v>5</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>28-03-2027 18:05:34</t>
-        </is>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P37" t="n">
-        <v>77276</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2882,27 +2896,27 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>112240</v>
+        <v>112246</v>
       </c>
       <c r="C38" t="n">
-        <v>326427</v>
+        <v>386941</v>
       </c>
       <c r="D38" t="n">
-        <v>23366</v>
+        <v>29098</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ANABEL GÓMEZ  RAMOS</t>
+          <t>FABIOLA  PLAZA  CARMONA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>STA CATARINA</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>01-10-2026 9:30:16</t>
+          <t>01-10-2026 11:04:12</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2924,14 +2938,14 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>599</v>
+        <v>849</v>
       </c>
       <c r="M38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>30-03-2027 9:30:16</t>
+          <t>26-09-2027 11:04:12</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2947,29 +2961,27 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>112257</v>
+        <v>112296</v>
       </c>
       <c r="C39" t="n">
-        <v>5992</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>04930</t>
-        </is>
+        <v>387909</v>
+      </c>
+      <c r="D39" t="n">
+        <v>30066</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>JAZMIN GUADALUPE ARELLANOS SAUCEDA</t>
+          <t>CESAR JOSUE  ROJO  OSORIO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AZAHARES CUL</t>
+          <t>SAN ISIDRO CUL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>01-10-2026 13:46:44</t>
+          <t>01-10-2026 19:22:26</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2991,19 +3003,17 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>599</v>
-      </c>
-      <c r="M39" t="n">
-        <v>5</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>30-03-2027 13:46:44</t>
-        </is>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -3014,17 +3024,17 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>112287</v>
+        <v>112331</v>
       </c>
       <c r="C40" t="n">
-        <v>330617</v>
+        <v>163266</v>
       </c>
       <c r="D40" t="n">
-        <v>15671</v>
+        <v>60799</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAMIRO MARTINEZ RAMIREZ</t>
+          <t>FERNANDO DAVID HERNANDEZ RAMIREZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3034,12 +3044,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>01-10-2026 18:35:12</t>
+          <t>02-10-2026 17:07:05</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -3063,7 +3073,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>26-09-2027 18:35:12</t>
+          <t>27-09-2027 17:07:05</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3079,27 +3089,27 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>112271</v>
+        <v>112243</v>
       </c>
       <c r="C41" t="n">
-        <v>387846</v>
+        <v>118726</v>
       </c>
       <c r="D41" t="n">
-        <v>30003</v>
+        <v>16436</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MARIA CRISTINA GARCIA GOMEZ</t>
+          <t>JONATHAN BERNAL REYNA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>01-10-2026 16:57:21</t>
+          <t>01-10-2026 9:47:38</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3121,17 +3131,19 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>949</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>30-03-2027 9:47:38</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -3142,27 +3154,27 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>112267</v>
+        <v>112261</v>
       </c>
       <c r="C42" t="n">
-        <v>339819</v>
+        <v>387404</v>
       </c>
       <c r="D42" t="n">
-        <v>17637</v>
+        <v>29561</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TOBIAS FREIDTAINS FREIDTAINS</t>
+          <t>CELENE VILLANUEVA  BRIONES</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>01-10-2026 16:52:34</t>
+          <t>01-10-2026 14:57:54</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3184,7 +3196,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>799</v>
+        <v>949</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3205,32 +3217,32 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>112315</v>
+        <v>112295</v>
       </c>
       <c r="C43" t="n">
-        <v>387966</v>
+        <v>347831</v>
       </c>
       <c r="D43" t="n">
-        <v>30123</v>
+        <v>89996</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MAURICIO MACIAS SILLER</t>
+          <t>CARLOS ALBERTO LOPEZ ALARCON</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>02-10-2026 10:56:58</t>
+          <t>01-10-2026 19:21:26</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3243,24 +3255,28 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>949</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+        <v>699</v>
+      </c>
+      <c r="M43" t="n">
+        <v>5</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>30-03-2027 19:21:26</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>95613</v>
+      </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -3268,27 +3284,27 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>111012</v>
+        <v>112276</v>
       </c>
       <c r="C44" t="n">
-        <v>68471</v>
+        <v>90016</v>
       </c>
       <c r="D44" t="n">
-        <v>66299</v>
+        <v>87793</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>JESUS MAURICIO VALTIERRA HERNANDEZ</t>
+          <t>FRANCISCO GONZALEZ CHARLES</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>15-09-2026 19:54:08</t>
+          <t>01-10-2026 17:27:02</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3306,18 +3322,18 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M44" t="n">
         <v>11</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>10-09-2027 19:54:08</t>
+          <t>26-09-2027 17:27:02</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3325,9 +3341,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P44" t="n">
-        <v>102987</v>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3335,19 +3349,17 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>110103</v>
+        <v>112326</v>
       </c>
       <c r="C45" t="n">
-        <v>202835</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>00343</t>
-        </is>
+        <v>229384</v>
+      </c>
+      <c r="D45" t="n">
+        <v>26889</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CRISTOBAL TIRADO CASTAÑEDA</t>
+          <t>JOSE MIGUEL  MOSQUEDA MONTIEL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3357,7 +3369,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>02-09-2026 11:12:05</t>
+          <t>02-10-2026 13:50:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3375,18 +3387,18 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>499</v>
+        <v>599</v>
       </c>
       <c r="M45" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>28-08-2027 11:12:05</t>
+          <t>31-03-2027 13:50:00</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3394,9 +3406,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P45" t="n">
-        <v>91359</v>
-      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -3404,32 +3414,32 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>110104</v>
+        <v>110100</v>
       </c>
       <c r="C46" t="n">
-        <v>129528</v>
+        <v>289981</v>
       </c>
       <c r="D46" t="n">
-        <v>27196</v>
+        <v>87479</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MARCO ANTONIO BARRAZA  PAREDES</t>
+          <t>RICARDO HERNANDEZ CASTILLO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SEND CHIH</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>02-09-2026 11:17:33</t>
+          <t>02-09-2026 10:19:32</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3446,14 +3456,14 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>399</v>
+        <v>499</v>
       </c>
       <c r="M46" t="n">
         <v>11</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>28-08-2027 11:17:33</t>
+          <t>28-08-2027 10:19:32</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3462,7 +3472,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>66241</v>
+        <v>107633</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
@@ -3471,27 +3481,27 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>112258</v>
+        <v>111587</v>
       </c>
       <c r="C47" t="n">
-        <v>350328</v>
+        <v>339078</v>
       </c>
       <c r="D47" t="n">
-        <v>92492</v>
+        <v>16896</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PAMELA RODRIGUEZ N</t>
+          <t>PEDRO  MORALEZ  ESPARZA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>01-10-2026 14:03:38</t>
+          <t>22-09-2026 18:35:31</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3509,7 +3519,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -3520,7 +3530,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>26-09-2027 14:03:38</t>
+          <t>17-09-2027 18:35:31</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3528,7 +3538,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>91215</v>
+      </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3536,27 +3548,29 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>112294</v>
+        <v>112289</v>
       </c>
       <c r="C48" t="n">
-        <v>387904</v>
-      </c>
-      <c r="D48" t="n">
-        <v>30061</v>
+        <v>9780</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>08709</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>LAISHA AMAIRAMI DOMINGUEZ GARCIA</t>
+          <t>CONSUELO MUÑOZ ROSALES</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SAN ISIDRO CUL</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>01-10-2026 19:16:44</t>
+          <t>01-10-2026 18:43:56</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3578,17 +3592,19 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>699</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+        <v>999</v>
+      </c>
+      <c r="M48" t="n">
+        <v>11</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>26-09-2027 18:43:56</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -3599,32 +3615,32 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>112270</v>
+        <v>112323</v>
       </c>
       <c r="C49" t="n">
-        <v>385596</v>
+        <v>382611</v>
       </c>
       <c r="D49" t="n">
-        <v>27753</v>
+        <v>24768</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>LUIS GIOVANNIE GARCIA  HERNADEZ</t>
+          <t>ALMA ANGELINA  GALVEZ  DOMINGUEZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>01-10-2026 16:55:45</t>
+          <t>02-10-2026 13:02:32</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01-01-2027 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3637,26 +3653,26 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1549</v>
-      </c>
-      <c r="M49" t="n">
-        <v>9</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>26-09-2027 16:55:45</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>110182</v>
+      </c>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -3664,27 +3680,27 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>112293</v>
+        <v>112265</v>
       </c>
       <c r="C50" t="n">
-        <v>134981</v>
+        <v>387835</v>
       </c>
       <c r="D50" t="n">
-        <v>32629</v>
+        <v>29992</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA  RAMON  DE LA CRUZ</t>
+          <t>VICTOR MARCELO CORTINAS FLORES</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>01-10-2026 19:11:32</t>
+          <t>01-10-2026 16:15:24</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3706,14 +3722,14 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>599</v>
+        <v>849</v>
       </c>
       <c r="M50" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>30-03-2027 19:11:32</t>
+          <t>26-09-2027 16:15:24</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3729,17 +3745,17 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>112302</v>
+        <v>112312</v>
       </c>
       <c r="C51" t="n">
-        <v>351343</v>
+        <v>156642</v>
       </c>
       <c r="D51" t="n">
-        <v>93507</v>
+        <v>54186</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ASTRID ESTHEFANY ORGEN  OBESO</t>
+          <t>MARIA DEL ROCIO  RODRIGUEZ  FELIX</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3749,12 +3765,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>01-10-2026 20:10:26</t>
+          <t>02-10-2026 10:15:11</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3771,19 +3787,17 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>599</v>
-      </c>
-      <c r="M51" t="n">
-        <v>5</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>30-03-2027 20:10:26</t>
-        </is>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -3794,32 +3808,32 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>112238</v>
+        <v>112365</v>
       </c>
       <c r="C52" t="n">
-        <v>36177</v>
+        <v>388131</v>
       </c>
       <c r="D52" t="n">
-        <v>34091</v>
+        <v>30288</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DENISSE  VARGAS MARTINEZZ</t>
+          <t>SERGIO  RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>01-10-2026 8:10:41</t>
+          <t>03-10-2026 9:34:15</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3832,26 +3846,26 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>599</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M52" t="n">
+        <v>11</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>28-09-2027 9:34:15</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P52" t="n">
-        <v>53295</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -3859,32 +3873,32 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>112304</v>
+        <v>112273</v>
       </c>
       <c r="C53" t="n">
-        <v>387933</v>
+        <v>387843</v>
       </c>
       <c r="D53" t="n">
-        <v>30090</v>
+        <v>30000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ALISON ORTEGA GOMEZ</t>
+          <t>GUADALUPE JAVIER CHAPA  HERRERA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>02-10-2026 6:15:03</t>
+          <t>01-10-2026 17:02:04</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3901,19 +3915,17 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>549</v>
-      </c>
-      <c r="M53" t="n">
-        <v>11</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>27-09-2027 6:15:03</t>
-        </is>
-      </c>
+        <v>949</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
@@ -3924,32 +3936,32 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>112253</v>
+        <v>112346</v>
       </c>
       <c r="C54" t="n">
-        <v>387797</v>
+        <v>22960</v>
       </c>
       <c r="D54" t="n">
-        <v>29954</v>
+        <v>21854</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>JOSHA JANDRY  BELLO  GONZALEZ</t>
+          <t>ANABEL  VALDENEGRO  MEJIA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>01-10-2026 13:06:16</t>
+          <t>02-10-2026 18:24:47</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3966,14 +3978,14 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>649</v>
+        <v>599</v>
       </c>
       <c r="M54" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>26-09-2027 13:06:16</t>
+          <t>31-03-2027 18:24:47</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -3989,32 +4001,32 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>112292</v>
+        <v>110273</v>
       </c>
       <c r="C55" t="n">
-        <v>386711</v>
+        <v>331811</v>
       </c>
       <c r="D55" t="n">
-        <v>28868</v>
+        <v>16615</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ANA DELIA  LOPEZ  NIEBLAS</t>
+          <t>LUIS EDUARDO BENITEZ BATHEN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>01-10-2026 19:10:21</t>
+          <t>05-09-2026 10:22:27</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>04-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -4027,18 +4039,18 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>599</v>
+        <v>649</v>
       </c>
       <c r="M55" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>30-03-2027 19:10:21</t>
+          <t>31-08-2027 10:22:27</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4046,7 +4058,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>85520</v>
+      </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -4054,32 +4068,32 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>112310</v>
+        <v>112268</v>
       </c>
       <c r="C56" t="n">
-        <v>387950</v>
+        <v>387603</v>
       </c>
       <c r="D56" t="n">
-        <v>30107</v>
+        <v>29760</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>GABRIEL TREJO CAMACHO</t>
+          <t>ALEXIS TERRAZA VALENZUELA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>02-10-2026 8:42:40</t>
+          <t>01-10-2026 16:52:36</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -4096,14 +4110,14 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>849</v>
+        <v>599</v>
       </c>
       <c r="M56" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>27-09-2027 8:42:40</t>
+          <t>30-03-2027 16:52:36</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4119,32 +4133,32 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>112280</v>
+        <v>112359</v>
       </c>
       <c r="C57" t="n">
-        <v>125817</v>
+        <v>388112</v>
       </c>
       <c r="D57" t="n">
-        <v>23492</v>
+        <v>30269</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ALEJANDRO  ARREDONDO BOJORQUEZ</t>
+          <t>JENNIFER EHUNICE CAMACHO VARO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>01-10-2026 18:03:34</t>
+          <t>03-10-2026 7:32:36</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -4157,26 +4171,26 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>699</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M57" t="n">
+        <v>5</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>01-04-2027 7:32:36</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P57" t="n">
-        <v>43718</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -4184,27 +4198,27 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>112300</v>
+        <v>112248</v>
       </c>
       <c r="C58" t="n">
-        <v>387867</v>
+        <v>67098</v>
       </c>
       <c r="D58" t="n">
-        <v>30024</v>
+        <v>64929</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>GUADALUPE GEORGINA  GONZALEZ CIRIGO</t>
+          <t>JARI BLANCARTE CASTRO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>01-10-2026 19:36:27</t>
+          <t>01-10-2026 11:45:13</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4222,18 +4236,18 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>649</v>
+        <v>599</v>
       </c>
       <c r="M58" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>26-09-2027 19:36:27</t>
+          <t>30-03-2027 11:45:13</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4249,17 +4263,17 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>112187</v>
+        <v>112279</v>
       </c>
       <c r="C59" t="n">
-        <v>164685</v>
+        <v>277374</v>
       </c>
       <c r="D59" t="n">
-        <v>62218</v>
+        <v>74875</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OSCAR EDCARDA GUZMAN GONZALEZ</t>
+          <t>MARIA ISABEL SOJO REYNAGA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4269,12 +4283,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>30-09-2026 15:16:45</t>
+          <t>01-10-2026 17:59:41</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>04-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -4287,26 +4301,26 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>549</v>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+      <c r="M59" t="n">
+        <v>11</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>26-09-2027 17:59:41</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P59" t="n">
-        <v>102910</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -4314,29 +4328,27 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>110106</v>
+        <v>112253</v>
       </c>
       <c r="C60" t="n">
-        <v>204657</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>02165</t>
-        </is>
+        <v>387797</v>
+      </c>
+      <c r="D60" t="n">
+        <v>29954</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ERANDI LIZBETH CRUZ  CASTILLO</t>
+          <t>JOSHA JANDRY  BELLO  GONZALEZ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>02-09-2026 13:25:36</t>
+          <t>01-10-2026 13:06:16</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4354,18 +4366,18 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>399</v>
+        <v>649</v>
       </c>
       <c r="M60" t="n">
         <v>11</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>28-08-2027 13:25:36</t>
+          <t>26-09-2027 13:06:16</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4373,9 +4385,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P60" t="n">
-        <v>7977</v>
-      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -4383,27 +4393,27 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>112263</v>
+        <v>112292</v>
       </c>
       <c r="C61" t="n">
-        <v>387820</v>
+        <v>386711</v>
       </c>
       <c r="D61" t="n">
-        <v>29977</v>
+        <v>28868</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RICARDO RAMIREZ  MARTINEZ</t>
+          <t>ANA DELIA  LOPEZ  NIEBLAS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>01-10-2026 15:26:38</t>
+          <t>01-10-2026 19:10:21</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4432,7 +4442,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>30-03-2027 15:26:38</t>
+          <t>30-03-2027 19:10:21</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4448,32 +4458,32 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>112299</v>
+        <v>112310</v>
       </c>
       <c r="C62" t="n">
-        <v>387908</v>
+        <v>387950</v>
       </c>
       <c r="D62" t="n">
-        <v>30065</v>
+        <v>30107</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ERIKA NATCHA MARTINEZ ANTONIO</t>
+          <t>GABRIEL TREJO CAMACHO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>01-10-2026 19:28:17</t>
+          <t>02-10-2026 8:42:40</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -4490,14 +4500,14 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>599</v>
+        <v>849</v>
       </c>
       <c r="M62" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>30-03-2027 19:28:17</t>
+          <t>27-09-2027 8:42:40</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4513,32 +4523,32 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>112237</v>
+        <v>112332</v>
       </c>
       <c r="C63" t="n">
-        <v>387278</v>
+        <v>388016</v>
       </c>
       <c r="D63" t="n">
-        <v>29435</v>
+        <v>30173</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ANA ABIGAIL GUILLEN ENRIQUEZ</t>
+          <t>JOSE IGNACIO  AGUIRRE  HERNANDEZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>01-10-2026 7:46:21</t>
+          <t>02-10-2026 17:08:40</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -4562,7 +4572,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>26-09-2027 7:46:21</t>
+          <t>27-09-2027 17:08:40</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4578,32 +4588,32 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>112322</v>
+        <v>112364</v>
       </c>
       <c r="C64" t="n">
-        <v>387986</v>
+        <v>215600</v>
       </c>
       <c r="D64" t="n">
-        <v>30143</v>
+        <v>13108</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MANUELA DE JESUS RUIZ ALUCANO</t>
+          <t>VERONICA LUCIA ALVAREZ ZAVALA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>02-10-2026 13:00:38</t>
+          <t>03-10-2026 9:02:37</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -4616,18 +4626,18 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>549</v>
+        <v>699</v>
       </c>
       <c r="M64" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>27-09-2027 13:00:38</t>
+          <t>01-04-2027 9:02:37</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4635,7 +4645,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>54458</v>
+      </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -4643,34 +4655,34 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>110818</v>
+        <v>110103</v>
       </c>
       <c r="C65" t="n">
-        <v>312013</v>
+        <v>202835</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>09512</t>
+          <t>00343</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>JESUS GUSTAVO MARQUEZ GONZALEZ</t>
+          <t>CRISTOBAL TIRADO CASTAÑEDA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>14-09-2026 15:17:57</t>
+          <t>02-09-2026 11:12:05</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -4694,7 +4706,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>09-09-2027 15:17:57</t>
+          <t>28-08-2027 11:12:05</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -4703,7 +4715,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>76787</v>
+        <v>91359</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
@@ -4712,32 +4724,32 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>112278</v>
+        <v>112270</v>
       </c>
       <c r="C66" t="n">
-        <v>387863</v>
+        <v>385596</v>
       </c>
       <c r="D66" t="n">
-        <v>30020</v>
+        <v>27753</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FERNANDO  MANRIQUE MELLADO</t>
+          <t>LUIS GIOVANNIE GARCIA  HERNADEZ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>01-10-2026 17:43:45</t>
+          <t>01-10-2026 16:55:45</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>01-01-2027 23:59:59</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4754,17 +4766,19 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>549</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+        <v>1549</v>
+      </c>
+      <c r="M66" t="n">
+        <v>9</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>26-09-2027 16:55:45</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -4775,27 +4789,27 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>112298</v>
+        <v>112293</v>
       </c>
       <c r="C67" t="n">
-        <v>387453</v>
+        <v>134981</v>
       </c>
       <c r="D67" t="n">
-        <v>29610</v>
+        <v>32629</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MARCELA GOMEZ DEANDAR</t>
+          <t>MARIA FERNANDA  RAMON  DE LA CRUZ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>01-10-2026 19:27:30</t>
+          <t>01-10-2026 19:11:32</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4817,14 +4831,14 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>849</v>
+        <v>599</v>
       </c>
       <c r="M67" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>26-09-2027 19:27:30</t>
+          <t>30-03-2027 19:11:32</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -4840,27 +4854,27 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>112268</v>
+        <v>112302</v>
       </c>
       <c r="C68" t="n">
-        <v>387603</v>
+        <v>351343</v>
       </c>
       <c r="D68" t="n">
-        <v>29760</v>
+        <v>93507</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ALEXIS TERRAZA VALENZUELA</t>
+          <t>ASTRID ESTHEFANY ORGEN  OBESO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>AZAHARES CUL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>01-10-2026 16:52:36</t>
+          <t>01-10-2026 20:10:26</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4889,7 +4903,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>30-03-2027 16:52:36</t>
+          <t>30-03-2027 20:10:26</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -4905,32 +4919,32 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>112273</v>
+        <v>112336</v>
       </c>
       <c r="C69" t="n">
-        <v>387843</v>
+        <v>172829</v>
       </c>
       <c r="D69" t="n">
-        <v>30000</v>
+        <v>70348</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>GUADALUPE JAVIER CHAPA  HERRERA</t>
+          <t>EVA ELIZABETH ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SEND CHIH</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>01-10-2026 17:02:04</t>
+          <t>02-10-2026 17:24:08</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4947,17 +4961,19 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>949</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M69" t="n">
+        <v>11</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>27-09-2027 17:24:08</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -4968,32 +4984,32 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>112248</v>
+        <v>110104</v>
       </c>
       <c r="C70" t="n">
-        <v>67098</v>
+        <v>129528</v>
       </c>
       <c r="D70" t="n">
-        <v>64929</v>
+        <v>27196</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>JARI BLANCARTE CASTRO</t>
+          <t>MARCO ANTONIO BARRAZA  PAREDES</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>SEND CHIH</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>01-10-2026 11:45:13</t>
+          <t>02-09-2026 11:17:33</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -5006,18 +5022,18 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>CANCELADO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>599</v>
+        <v>399</v>
       </c>
       <c r="M70" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>30-03-2027 11:45:13</t>
+          <t>28-08-2027 11:17:33</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5025,7 +5041,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>66241</v>
+      </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -5033,32 +5051,34 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>112279</v>
+        <v>111397</v>
       </c>
       <c r="C71" t="n">
-        <v>277374</v>
-      </c>
-      <c r="D71" t="n">
-        <v>74875</v>
+        <v>361169</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>03334</t>
+        </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MARIA ISABEL SOJO REYNAGA</t>
+          <t>SONIA LOPEZ  RUIZ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>01-10-2026 17:59:41</t>
+          <t>21-09-2026 17:26:29</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>04-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -5071,26 +5091,26 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>549</v>
-      </c>
-      <c r="M71" t="n">
-        <v>11</v>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>26-09-2027 17:59:41</t>
-        </is>
-      </c>
+        <v>799</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>100529</v>
+      </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -5098,27 +5118,27 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>112252</v>
+        <v>112258</v>
       </c>
       <c r="C72" t="n">
-        <v>200980</v>
+        <v>350328</v>
       </c>
       <c r="D72" t="n">
-        <v>98487</v>
+        <v>92492</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>JOSE ARTURO HURTADO ESQUER</t>
+          <t>PAMELA RODRIGUEZ N</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>01-10-2026 12:52:41</t>
+          <t>01-10-2026 14:03:38</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5136,18 +5156,18 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>699</v>
+        <v>649</v>
       </c>
       <c r="M72" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>30-03-2027 12:52:41</t>
+          <t>26-09-2027 14:03:38</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5155,9 +5175,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P72" t="n">
-        <v>10528</v>
-      </c>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -5165,27 +5183,27 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>112277</v>
+        <v>112294</v>
       </c>
       <c r="C73" t="n">
-        <v>387864</v>
+        <v>387904</v>
       </c>
       <c r="D73" t="n">
-        <v>30021</v>
+        <v>30061</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>JESUS JULIAN GALLEGOS HERREEA</t>
+          <t>LAISHA AMAIRAMI DOMINGUEZ GARCIA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>SAN ISIDRO CUL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>01-10-2026 17:42:25</t>
+          <t>01-10-2026 19:16:44</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5207,19 +5225,17 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>549</v>
-      </c>
-      <c r="M73" t="n">
-        <v>11</v>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>26-09-2027 17:42:25</t>
-        </is>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -5230,32 +5246,32 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>112284</v>
+        <v>112337</v>
       </c>
       <c r="C74" t="n">
-        <v>387872</v>
+        <v>388027</v>
       </c>
       <c r="D74" t="n">
-        <v>30029</v>
+        <v>30184</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MONSERRAT  SAVAAVEDRA  ROJAS</t>
+          <t>MARTHA KARINA LOPEZ  ALQUICIRA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>01-10-2026 18:20:28</t>
+          <t>02-10-2026 17:30:59</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-01-2027 23:59:59</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -5272,17 +5288,19 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>549</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+        <v>1549</v>
+      </c>
+      <c r="M74" t="n">
+        <v>9</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>27-09-2027 17:30:59</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -5293,27 +5311,27 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>112318</v>
+        <v>112238</v>
       </c>
       <c r="C75" t="n">
-        <v>387972</v>
+        <v>36177</v>
       </c>
       <c r="D75" t="n">
-        <v>30129</v>
+        <v>34091</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>NANCY  REMIGIO ARZATE</t>
+          <t>DENISSE  VARGAS MARTINEZZ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>02-10-2026 11:31:57</t>
+          <t>01-10-2026 8:10:41</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5331,26 +5349,26 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>699</v>
-      </c>
-      <c r="M75" t="n">
-        <v>5</v>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>31-03-2027 11:31:57</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>53295</v>
+      </c>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -5358,17 +5376,17 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>112301</v>
+        <v>112304</v>
       </c>
       <c r="C76" t="n">
-        <v>157985</v>
+        <v>387933</v>
       </c>
       <c r="D76" t="n">
-        <v>55528</v>
+        <v>30090</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>JOHANA JAQUELINE RAMOS ELIZALDE</t>
+          <t>ALISON ORTEGA GOMEZ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5378,12 +5396,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>01-10-2026 20:07:43</t>
+          <t>02-10-2026 6:15:03</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -5396,18 +5414,18 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>699</v>
+        <v>549</v>
       </c>
       <c r="M76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>30-03-2027 20:07:43</t>
+          <t>27-09-2027 6:15:03</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5415,9 +5433,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P76" t="n">
-        <v>68615</v>
-      </c>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -5425,32 +5441,32 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>112234</v>
+        <v>112340</v>
       </c>
       <c r="C77" t="n">
-        <v>386565</v>
+        <v>388031</v>
       </c>
       <c r="D77" t="n">
-        <v>28722</v>
+        <v>30188</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>JOSE ARMANDO BARAJAS GONGORA</t>
+          <t>JOEL AURELIO  MEJIA  AGUILAR</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>01-10-2026 6:16:40</t>
+          <t>02-10-2026 17:39:50</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -5467,17 +5483,19 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>949</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M77" t="n">
+        <v>5</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>31-03-2027 17:39:50</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P77" t="inlineStr"/>
@@ -5488,32 +5506,32 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>110534</v>
+        <v>112280</v>
       </c>
       <c r="C78" t="n">
-        <v>376238</v>
+        <v>125817</v>
       </c>
       <c r="D78" t="n">
-        <v>18398</v>
+        <v>23492</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RUBEN ALBERTO  GUIZAR  CAMACHO</t>
+          <t>ALEJANDRO  ARREDONDO BOJORQUEZ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>08-09-2026 20:16:38</t>
+          <t>01-10-2026 18:03:34</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>28-10-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -5530,7 +5548,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>599</v>
+        <v>699</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -5544,7 +5562,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>107294</v>
+        <v>43718</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
@@ -5553,32 +5571,34 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>112249</v>
+        <v>112347</v>
       </c>
       <c r="C79" t="n">
-        <v>387788</v>
-      </c>
-      <c r="D79" t="n">
-        <v>29945</v>
+        <v>104900</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>02647</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA PIGNI RIMOLDI</t>
+          <t>JORGE VALENCIA CALDERON</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>01-10-2026 11:52:36</t>
+          <t>02-10-2026 18:35:24</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -5591,24 +5611,28 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>799</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+        <v>699</v>
+      </c>
+      <c r="M79" t="n">
+        <v>5</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>31-03-2027 18:35:24</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>73428</v>
+      </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
@@ -5616,17 +5640,17 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>112313</v>
+        <v>112271</v>
       </c>
       <c r="C80" t="n">
-        <v>386133</v>
+        <v>387846</v>
       </c>
       <c r="D80" t="n">
-        <v>28290</v>
+        <v>30003</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>LAURA LETICIA ESPARZA MARTINEZ</t>
+          <t>MARIA CRISTINA GARCIA GOMEZ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5636,12 +5660,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>02-10-2026 10:20:26</t>
+          <t>01-10-2026 16:57:21</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -5679,27 +5703,27 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>112235</v>
+        <v>112267</v>
       </c>
       <c r="C81" t="n">
-        <v>387285</v>
+        <v>339819</v>
       </c>
       <c r="D81" t="n">
-        <v>29442</v>
+        <v>17637</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CAMILA CERRILLO ESTRADA</t>
+          <t>TOBIAS FREIDTAINS FREIDTAINS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>01-10-2026 7:29:03</t>
+          <t>01-10-2026 16:52:34</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5721,7 +5745,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>949</v>
+        <v>799</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -5742,32 +5766,32 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>112285</v>
+        <v>112328</v>
       </c>
       <c r="C82" t="n">
-        <v>387877</v>
+        <v>388010</v>
       </c>
       <c r="D82" t="n">
-        <v>30034</v>
+        <v>30167</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>GRACIELA VARGAS OCHOA</t>
+          <t>GENOVA  LEDESMA ZETINA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>01-10-2026 18:27:20</t>
+          <t>02-10-2026 16:39:59</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -5784,17 +5808,19 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>549</v>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+        <v>849</v>
+      </c>
+      <c r="M82" t="n">
+        <v>11</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>27-09-2027 16:39:59</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -5805,32 +5831,32 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>112247</v>
+        <v>112353</v>
       </c>
       <c r="C83" t="n">
-        <v>387785</v>
+        <v>93971</v>
       </c>
       <c r="D83" t="n">
-        <v>29942</v>
+        <v>91730</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>GERARDO GONZALEZ REBOLLOSO</t>
+          <t>GILBERTO ALEJANDRO VALENZUELA MEZA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>01-10-2026 11:33:27</t>
+          <t>02-10-2026 20:48:51</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -5847,17 +5873,19 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>949</v>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M83" t="n">
+        <v>11</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>27-09-2027 20:48:51</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -5868,32 +5896,32 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>112297</v>
+        <v>112360</v>
       </c>
       <c r="C84" t="n">
-        <v>347840</v>
+        <v>388114</v>
       </c>
       <c r="D84" t="n">
-        <v>90005</v>
+        <v>30271</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SANTIAGO LOPEZ MALVAEZ</t>
+          <t>LIZZY CARELI CAMACHO VARO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>01-10-2026 19:25:55</t>
+          <t>03-10-2026 7:41:13</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -5917,7 +5945,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>30-03-2027 19:25:55</t>
+          <t>01-04-2027 7:41:13</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -5933,27 +5961,27 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>112316</v>
+        <v>112349</v>
       </c>
       <c r="C85" t="n">
-        <v>387965</v>
+        <v>388071</v>
       </c>
       <c r="D85" t="n">
-        <v>30122</v>
+        <v>30228</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MARIEL LETICIA  MACIAS  ROMAN</t>
+          <t>REYNA CRUZ HUERTAS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>02-10-2026 11:00:28</t>
+          <t>02-10-2026 19:07:17</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5977,44 +6005,2951 @@
       <c r="L85" t="n">
         <v>699</v>
       </c>
-      <c r="M85" t="n">
-        <v>5</v>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>31-03-2027 11:00:28</t>
-        </is>
-      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Reporte generado: 02-10-2026 08:04 p. m.</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>112241</v>
+      </c>
+      <c r="C86" t="n">
+        <v>154646</v>
+      </c>
+      <c r="D86" t="n">
+        <v>52201</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>DAVID EMILIANO  MALDONADO  VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>01-10-2026 9:34:09</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>599</v>
+      </c>
+      <c r="M86" t="n">
+        <v>5</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>30-03-2027 9:34:09</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>112286</v>
+      </c>
+      <c r="C87" t="n">
+        <v>387878</v>
+      </c>
+      <c r="D87" t="n">
+        <v>30035</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>BRYAN ISRAEL GARCIA  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>01-10-2026 18:28:15</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>549</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>112350</v>
+      </c>
+      <c r="C88" t="n">
+        <v>388067</v>
+      </c>
+      <c r="D88" t="n">
+        <v>30224</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>GABRIEL  TELLEZ  CHANG</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>02-10-2026 19:11:38</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>03-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>549</v>
+      </c>
+      <c r="M88" t="n">
+        <v>11</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>27-09-2027 19:11:38</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>112327</v>
+      </c>
+      <c r="C89" t="n">
+        <v>387847</v>
+      </c>
+      <c r="D89" t="n">
+        <v>30004</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RAYMUNDO GARCIA FRAGOSO</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>02-10-2026 15:26:43</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>599</v>
+      </c>
+      <c r="M89" t="n">
+        <v>5</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>31-03-2027 15:26:43</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>112108</v>
+      </c>
+      <c r="C90" t="n">
+        <v>171319</v>
+      </c>
+      <c r="D90" t="n">
+        <v>68838</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>MARIA  DE JESUS CARDONA ALVARADO</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>29-09-2026 18:05:34</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>449</v>
+      </c>
+      <c r="M90" t="n">
+        <v>5</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>28-03-2027 18:05:34</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>77276</v>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>112333</v>
+      </c>
+      <c r="C91" t="n">
+        <v>388019</v>
+      </c>
+      <c r="D91" t="n">
+        <v>30176</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>JESUS ALFREDO  SAUCEDO  HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>02-10-2026 17:11:11</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>549</v>
+      </c>
+      <c r="M91" t="n">
+        <v>11</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>27-09-2027 17:11:11</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>112240</v>
+      </c>
+      <c r="C92" t="n">
+        <v>326427</v>
+      </c>
+      <c r="D92" t="n">
+        <v>23366</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ANABEL GÓMEZ  RAMOS</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>01-10-2026 9:30:16</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>599</v>
+      </c>
+      <c r="M92" t="n">
+        <v>5</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>30-03-2027 9:30:16</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>112257</v>
+      </c>
+      <c r="C93" t="n">
+        <v>5992</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>04930</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>JAZMIN GUADALUPE ARELLANOS SAUCEDA</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>01-10-2026 13:46:44</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>599</v>
+      </c>
+      <c r="M93" t="n">
+        <v>5</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>30-03-2027 13:46:44</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>112287</v>
+      </c>
+      <c r="C94" t="n">
+        <v>330617</v>
+      </c>
+      <c r="D94" t="n">
+        <v>15671</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RAMIRO MARTINEZ RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>01-10-2026 18:35:12</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>549</v>
+      </c>
+      <c r="M94" t="n">
+        <v>11</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>26-09-2027 18:35:12</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>112338</v>
+      </c>
+      <c r="C95" t="n">
+        <v>388028</v>
+      </c>
+      <c r="D95" t="n">
+        <v>30185</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ANDREA  GALINDO  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>02-10-2026 17:31:25</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>02-01-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M95" t="n">
+        <v>9</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>27-09-2027 17:31:25</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>111012</v>
+      </c>
+      <c r="C96" t="n">
+        <v>68471</v>
+      </c>
+      <c r="D96" t="n">
+        <v>66299</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>JESUS MAURICIO VALTIERRA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>15-09-2026 19:54:08</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>499</v>
+      </c>
+      <c r="M96" t="n">
+        <v>11</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>10-09-2027 19:54:08</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>102987</v>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>112315</v>
+      </c>
+      <c r="C97" t="n">
+        <v>387966</v>
+      </c>
+      <c r="D97" t="n">
+        <v>30123</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>MAURICIO MACIAS SILLER</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>02-10-2026 10:56:58</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>949</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>112329</v>
+      </c>
+      <c r="C98" t="n">
+        <v>388012</v>
+      </c>
+      <c r="D98" t="n">
+        <v>30169</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  GARELLI LEDESMA</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>02-10-2026 16:45:25</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>849</v>
+      </c>
+      <c r="M98" t="n">
+        <v>11</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>27-09-2027 16:45:25</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>112348</v>
+      </c>
+      <c r="C99" t="n">
+        <v>241357</v>
+      </c>
+      <c r="D99" t="n">
+        <v>38862</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>MARIA LUCERO PASTOR OLIVERA</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>02-10-2026 19:00:07</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>699</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>112290</v>
+      </c>
+      <c r="C100" t="n">
+        <v>387881</v>
+      </c>
+      <c r="D100" t="n">
+        <v>30038</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ALFREDO QUEZADA CURIEL</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>01-10-2026 18:44:30</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>999</v>
+      </c>
+      <c r="M100" t="n">
+        <v>11</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>26-09-2027 18:44:30</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>112307</v>
+      </c>
+      <c r="C101" t="n">
+        <v>387513</v>
+      </c>
+      <c r="D101" t="n">
+        <v>29670</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>LIZETH RAMIREZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>02-10-2026 7:13:03</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>649</v>
+      </c>
+      <c r="M101" t="n">
+        <v>11</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>27-09-2027 7:13:03</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>112339</v>
+      </c>
+      <c r="C102" t="n">
+        <v>388032</v>
+      </c>
+      <c r="D102" t="n">
+        <v>30189</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ARACELI LOPEZ  ALQUICIRA</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>02-10-2026 17:38:20</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>02-01-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>112354</v>
+      </c>
+      <c r="C103" t="n">
+        <v>386175</v>
+      </c>
+      <c r="D103" t="n">
+        <v>28332</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>PAULINA DEL CARMEN SANCHEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>02-10-2026 22:01:09</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>699</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>110227</v>
+      </c>
+      <c r="C104" t="n">
+        <v>382358</v>
+      </c>
+      <c r="D104" t="n">
+        <v>24515</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>MARISOL  ACUÑA VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>03-09-2026 21:18:41</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>649</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>110080</v>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>112309</v>
+      </c>
+      <c r="C105" t="n">
+        <v>383098</v>
+      </c>
+      <c r="D105" t="n">
+        <v>25255</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>BRENDA TAPIA CHAVEZ</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>02-10-2026 8:09:50</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>549</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>112311</v>
+      </c>
+      <c r="C106" t="n">
+        <v>387546</v>
+      </c>
+      <c r="D106" t="n">
+        <v>29703</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>LUIS FRANCISCO ORTEGA FRANCO</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>02-10-2026 9:43:43</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>599</v>
+      </c>
+      <c r="M106" t="n">
+        <v>5</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>31-03-2027 9:43:43</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>112325</v>
+      </c>
+      <c r="C107" t="n">
+        <v>387751</v>
+      </c>
+      <c r="D107" t="n">
+        <v>29908</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>MARI CRUZ JUAREZ LOPEZ</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>02-10-2026 13:45:09</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>849</v>
+      </c>
+      <c r="M107" t="n">
+        <v>11</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>27-09-2027 13:45:09</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>112269</v>
+      </c>
+      <c r="C108" t="n">
+        <v>387844</v>
+      </c>
+      <c r="D108" t="n">
+        <v>30001</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>DANIELA MONTSERRAT MARTINEZ  PLASCENCIA</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>01-10-2026 16:54:08</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>599</v>
+      </c>
+      <c r="M108" t="n">
+        <v>5</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>30-03-2027 16:54:08</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>112344</v>
+      </c>
+      <c r="C109" t="n">
+        <v>388041</v>
+      </c>
+      <c r="D109" t="n">
+        <v>30198</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>DIANA GUADALUPE URIAS RUIZ</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>02-10-2026 17:58:17</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>599</v>
+      </c>
+      <c r="M109" t="n">
+        <v>5</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>31-03-2027 17:58:17</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>111736</v>
+      </c>
+      <c r="C110" t="n">
+        <v>382132</v>
+      </c>
+      <c r="D110" t="n">
+        <v>24289</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>DAFNE VALERIA SARABIA  ALTAMIRANO</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>24-09-2026 15:01:07</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>30-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>599</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>109992</v>
+      </c>
+      <c r="Q110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>112272</v>
+      </c>
+      <c r="C111" t="n">
+        <v>387850</v>
+      </c>
+      <c r="D111" t="n">
+        <v>30007</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>PAMINGER FLORIAN  FLORIAN</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>01-10-2026 16:59:14</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>799</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>112330</v>
+      </c>
+      <c r="C112" t="n">
+        <v>388014</v>
+      </c>
+      <c r="D112" t="n">
+        <v>30171</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>FIORENZA GARELLI  LEDESMA</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>02-10-2026 16:49:48</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>849</v>
+      </c>
+      <c r="M112" t="n">
+        <v>11</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>27-09-2027 16:49:48</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>112324</v>
+      </c>
+      <c r="C113" t="n">
+        <v>387794</v>
+      </c>
+      <c r="D113" t="n">
+        <v>29951</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>ALAN ALI GARCIA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>02-10-2026 13:19:35</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>649</v>
+      </c>
+      <c r="M113" t="n">
+        <v>11</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>27-09-2027 13:19:35</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>112235</v>
+      </c>
+      <c r="C114" t="n">
+        <v>387285</v>
+      </c>
+      <c r="D114" t="n">
+        <v>29442</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>CAMILA CERRILLO ESTRADA</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>01-10-2026 7:29:03</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>949</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>112285</v>
+      </c>
+      <c r="C115" t="n">
+        <v>387877</v>
+      </c>
+      <c r="D115" t="n">
+        <v>30034</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>GRACIELA VARGAS OCHOA</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>01-10-2026 18:27:20</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>549</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>112249</v>
+      </c>
+      <c r="C116" t="n">
+        <v>387788</v>
+      </c>
+      <c r="D116" t="n">
+        <v>29945</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA PIGNI RIMOLDI</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>01-10-2026 11:52:36</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>799</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>112313</v>
+      </c>
+      <c r="C117" t="n">
+        <v>386133</v>
+      </c>
+      <c r="D117" t="n">
+        <v>28290</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>LAURA LETICIA ESPARZA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>02-10-2026 10:20:26</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>949</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>112252</v>
+      </c>
+      <c r="C118" t="n">
+        <v>200980</v>
+      </c>
+      <c r="D118" t="n">
+        <v>98487</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>JOSE ARTURO HURTADO ESQUER</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>01-10-2026 12:52:41</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>699</v>
+      </c>
+      <c r="M118" t="n">
+        <v>5</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>30-03-2027 12:52:41</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>10528</v>
+      </c>
+      <c r="Q118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>112277</v>
+      </c>
+      <c r="C119" t="n">
+        <v>387864</v>
+      </c>
+      <c r="D119" t="n">
+        <v>30021</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>JESUS JULIAN GALLEGOS HERREEA</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>01-10-2026 17:42:25</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>549</v>
+      </c>
+      <c r="M119" t="n">
+        <v>11</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>26-09-2027 17:42:25</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>112284</v>
+      </c>
+      <c r="C120" t="n">
+        <v>387872</v>
+      </c>
+      <c r="D120" t="n">
+        <v>30029</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>MONSERRAT  SAVAAVEDRA  ROJAS</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>01-10-2026 18:20:28</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>549</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>112318</v>
+      </c>
+      <c r="C121" t="n">
+        <v>387972</v>
+      </c>
+      <c r="D121" t="n">
+        <v>30129</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>NANCY  REMIGIO ARZATE</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>02-10-2026 11:31:57</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>699</v>
+      </c>
+      <c r="M121" t="n">
+        <v>5</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>31-03-2027 11:31:57</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>112234</v>
+      </c>
+      <c r="C122" t="n">
+        <v>386565</v>
+      </c>
+      <c r="D122" t="n">
+        <v>28722</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>JOSE ARMANDO BARAJAS GONGORA</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>01-10-2026 6:16:40</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>949</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>112301</v>
+      </c>
+      <c r="C123" t="n">
+        <v>157985</v>
+      </c>
+      <c r="D123" t="n">
+        <v>55528</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>JOHANA JAQUELINE RAMOS ELIZALDE</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>01-10-2026 20:07:43</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>699</v>
+      </c>
+      <c r="M123" t="n">
+        <v>5</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>30-03-2027 20:07:43</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>68615</v>
+      </c>
+      <c r="Q123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>112358</v>
+      </c>
+      <c r="C124" t="n">
+        <v>387752</v>
+      </c>
+      <c r="D124" t="n">
+        <v>29909</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL JUAREZ TLECUILE</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>03-10-2026 6:46:36</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>03-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>599</v>
+      </c>
+      <c r="M124" t="n">
+        <v>5</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>01-04-2027 6:46:36</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>110534</v>
+      </c>
+      <c r="C125" t="n">
+        <v>376238</v>
+      </c>
+      <c r="D125" t="n">
+        <v>18398</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>RUBEN ALBERTO  GUIZAR  CAMACHO</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>08-09-2026 20:16:38</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>28-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>599</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>107294</v>
+      </c>
+      <c r="Q125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>112355</v>
+      </c>
+      <c r="C126" t="n">
+        <v>386769</v>
+      </c>
+      <c r="D126" t="n">
+        <v>28926</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ALEXA DE MARIA SOTO  CHAVEZ</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>03-10-2026 6:06:53</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>03-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>849</v>
+      </c>
+      <c r="M126" t="n">
+        <v>11</v>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>28-09-2027 6:06:53</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>112247</v>
+      </c>
+      <c r="C127" t="n">
+        <v>387785</v>
+      </c>
+      <c r="D127" t="n">
+        <v>29942</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>GERARDO GONZALEZ REBOLLOSO</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>01-10-2026 11:33:27</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>949</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>112297</v>
+      </c>
+      <c r="C128" t="n">
+        <v>347840</v>
+      </c>
+      <c r="D128" t="n">
+        <v>90005</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>SANTIAGO LOPEZ MALVAEZ</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>01-10-2026 19:25:55</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>599</v>
+      </c>
+      <c r="M128" t="n">
+        <v>5</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>30-03-2027 19:25:55</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>112316</v>
+      </c>
+      <c r="C129" t="n">
+        <v>387965</v>
+      </c>
+      <c r="D129" t="n">
+        <v>30122</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>MARIEL LETICIA  MACIAS  ROMAN</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>02-10-2026 11:00:28</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>699</v>
+      </c>
+      <c r="M129" t="n">
+        <v>5</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>31-03-2027 11:00:28</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>112366</v>
+      </c>
+      <c r="C130" t="n">
+        <v>173672</v>
+      </c>
+      <c r="D130" t="n">
+        <v>71180</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AXEL  JIMENEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>03-10-2026 10:17:50</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>03-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>699</v>
+      </c>
+      <c r="M130" t="n">
+        <v>5</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>01-04-2027 10:17:50</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>80355</v>
+      </c>
+      <c r="Q130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Reporte generado: 03-10-2026 06:39 p. m.</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q131"/>
+  <dimension ref="A1:Q145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,32 +603,32 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>110250</v>
+        <v>110227</v>
       </c>
       <c r="C3" t="n">
-        <v>347993</v>
+        <v>382358</v>
       </c>
       <c r="D3" t="n">
-        <v>90158</v>
+        <v>24515</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VALERY MARISA HERNANDEZ  CASTILLO</t>
+          <t>MARISOL  ACUÑA VAZQUEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>04-09-2026 16:33:31</t>
+          <t>03-09-2026 21:18:41</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -645,23 +645,21 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>549</v>
-      </c>
-      <c r="M3" t="n">
-        <v>11</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>30-08-2027 16:33:31</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>95723</v>
+        <v>110080</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -670,27 +668,27 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>112342</v>
+        <v>112325</v>
       </c>
       <c r="C4" t="n">
-        <v>388034</v>
+        <v>387751</v>
       </c>
       <c r="D4" t="n">
-        <v>30191</v>
+        <v>29908</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RICARDO NOE  ZUÑIGA  PALACIOS</t>
+          <t>MARI CRUZ JUAREZ LOPEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02-10-2026 17:49:53</t>
+          <t>02-10-2026 13:45:09</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -712,14 +710,14 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>649</v>
+        <v>849</v>
       </c>
       <c r="M4" t="n">
         <v>11</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>27-09-2027 17:49:53</t>
+          <t>27-09-2027 13:45:09</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -735,27 +733,27 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>112281</v>
+        <v>112290</v>
       </c>
       <c r="C5" t="n">
-        <v>381005</v>
+        <v>387881</v>
       </c>
       <c r="D5" t="n">
-        <v>23163</v>
+        <v>30038</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RICARDO ALFREDO ARANDA DOWLING</t>
+          <t>ALFREDO QUEZADA CURIEL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01-10-2026 18:07:45</t>
+          <t>01-10-2026 18:44:30</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -777,17 +775,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>699</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>26-09-2027 18:44:30</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -798,32 +798,32 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>112363</v>
+        <v>112307</v>
       </c>
       <c r="C6" t="n">
-        <v>344891</v>
+        <v>387513</v>
       </c>
       <c r="D6" t="n">
-        <v>22708</v>
+        <v>29670</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DAVID CARLOS GALLARDO CONTRERAS</t>
+          <t>LIZETH RAMIREZ MARTINEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>03-10-2026 8:50:39</t>
+          <t>02-10-2026 7:13:03</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -836,18 +836,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>699</v>
+        <v>649</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>01-04-2027 8:50:39</t>
+          <t>27-09-2027 7:13:03</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -855,9 +855,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P6" t="n">
-        <v>106911</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -865,32 +863,32 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>112352</v>
+        <v>112339</v>
       </c>
       <c r="C7" t="n">
-        <v>388094</v>
+        <v>388032</v>
       </c>
       <c r="D7" t="n">
-        <v>30251</v>
+        <v>30189</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MIRIAM SELENE GARCIA POYORENA</t>
+          <t>ARACELI LOPEZ  ALQUICIRA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>02-10-2026 20:37:21</t>
+          <t>02-10-2026 17:38:20</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>02-01-2027 23:59:59</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -907,19 +905,17 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>599</v>
-      </c>
-      <c r="M7" t="n">
-        <v>5</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>31-03-2027 20:37:21</t>
-        </is>
-      </c>
+        <v>1549</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -930,27 +926,27 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112368</v>
+        <v>112354</v>
       </c>
       <c r="C8" t="n">
-        <v>387963</v>
+        <v>386175</v>
       </c>
       <c r="D8" t="n">
-        <v>30120</v>
+        <v>28332</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GIOVANNI ANTONIO VAZQUEZ RANGEL</t>
+          <t>PAULINA DEL CARMEN SANCHEZ CRUZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>02-10-2026 10:27:39</t>
+          <t>02-10-2026 22:01:09</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -993,32 +989,32 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>112244</v>
+        <v>112371</v>
       </c>
       <c r="C9" t="n">
-        <v>157095</v>
+        <v>387717</v>
       </c>
       <c r="D9" t="n">
-        <v>54639</v>
+        <v>29874</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MARIA DE LOURDES ALVARES PADILLA</t>
+          <t>YESENIA  RAMIREZ OZUA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>01-10-2026 10:15:02</t>
+          <t>03-10-2026 12:35:08</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>30-10-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1031,18 +1027,18 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="M9" t="n">
         <v>11</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>26-09-2027 10:15:02</t>
+          <t>28-09-2027 12:35:08</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1050,9 +1046,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>4233</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1060,32 +1054,32 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>112251</v>
+        <v>111736</v>
       </c>
       <c r="C10" t="n">
-        <v>387791</v>
+        <v>382132</v>
       </c>
       <c r="D10" t="n">
-        <v>29948</v>
+        <v>24289</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ANGEL GABRIEL RIVERA SALAZAR</t>
+          <t>DAFNE VALERIA SARABIA  ALTAMIRANO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>01-10-2026 12:36:00</t>
+          <t>24-09-2026 15:01:07</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>30-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1098,26 +1092,26 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>849</v>
-      </c>
-      <c r="M10" t="n">
-        <v>11</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>26-09-2027 12:36:00</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>109992</v>
+      </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1125,17 +1119,17 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>112319</v>
+        <v>112272</v>
       </c>
       <c r="C11" t="n">
-        <v>387974</v>
+        <v>387850</v>
       </c>
       <c r="D11" t="n">
-        <v>30131</v>
+        <v>30007</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UZIEL PICON  SOLIS</t>
+          <t>PAMINGER FLORIAN  FLORIAN</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1145,12 +1139,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>02-10-2026 11:58:57</t>
+          <t>01-10-2026 16:59:14</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>02-01-2027 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1167,19 +1161,17 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1549</v>
-      </c>
-      <c r="M11" t="n">
-        <v>9</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>27-09-2027 11:58:57</t>
-        </is>
-      </c>
+        <v>799</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1190,32 +1182,32 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>112362</v>
+        <v>112309</v>
       </c>
       <c r="C12" t="n">
-        <v>383624</v>
+        <v>383098</v>
       </c>
       <c r="D12" t="n">
-        <v>25781</v>
+        <v>25255</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DAYSI GUADALUPE SANTACRUZ RODRIGUEZ</t>
+          <t>BRENDA TAPIA CHAVEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>03-10-2026 8:45:37</t>
+          <t>02-10-2026 8:09:50</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1232,19 +1224,17 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>599</v>
-      </c>
-      <c r="M12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>01-04-2027 8:45:37</t>
-        </is>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1255,32 +1245,32 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>110251</v>
+        <v>112311</v>
       </c>
       <c r="C13" t="n">
-        <v>347990</v>
+        <v>387546</v>
       </c>
       <c r="D13" t="n">
-        <v>90155</v>
+        <v>29703</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LUIS ARTURO  HERNANDEZ  SALGADO</t>
+          <t>LUIS FRANCISCO ORTEGA FRANCO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>04-09-2026 16:36:08</t>
+          <t>02-10-2026 9:43:43</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1293,18 +1283,18 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>549</v>
+        <v>599</v>
       </c>
       <c r="M13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>30-08-2027 16:36:08</t>
+          <t>31-03-2027 9:43:43</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1312,9 +1302,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P13" t="n">
-        <v>95721</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1322,29 +1310,27 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>112274</v>
+        <v>112269</v>
       </c>
       <c r="C14" t="n">
-        <v>111039</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>08776</t>
-        </is>
+        <v>387844</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PEDRO MARIO  VALENZUELA  PINTO</t>
+          <t>DANIELA MONTSERRAT MARTINEZ  PLASCENCIA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AZAHARES CUL</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01-10-2026 17:03:49</t>
+          <t>01-10-2026 16:54:08</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1366,17 +1352,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>699</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>30-03-2027 16:54:08</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1387,32 +1375,32 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>110240</v>
+        <v>112344</v>
       </c>
       <c r="C15" t="n">
-        <v>90728</v>
+        <v>388041</v>
       </c>
       <c r="D15" t="n">
-        <v>88499</v>
+        <v>30198</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VALERIA V PEREZ VALDEZ</t>
+          <t>DIANA GUADALUPE URIAS RUIZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PABELLON RTO</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>04-09-2026 9:56:12</t>
+          <t>02-10-2026 17:58:17</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1425,26 +1413,26 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L15" t="n">
         <v>599</v>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>31-03-2027 17:58:17</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>107840</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1452,17 +1440,17 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>108953</v>
+        <v>112330</v>
       </c>
       <c r="C16" t="n">
-        <v>379812</v>
+        <v>388014</v>
       </c>
       <c r="D16" t="n">
-        <v>21970</v>
+        <v>30171</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>VICTOR  CORTINAS  FAVELA</t>
+          <t>FIORENZA GARELLI  LEDESMA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1472,12 +1460,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>18-08-2026 17:37:56</t>
+          <t>02-10-2026 16:49:48</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1490,7 +1478,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>CANCELADO</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1501,7 +1489,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>13-08-2027 17:37:56</t>
+          <t>27-09-2027 16:49:48</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1517,29 +1505,27 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>110818</v>
+        <v>112281</v>
       </c>
       <c r="C17" t="n">
-        <v>312013</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>09512</t>
-        </is>
+        <v>381005</v>
+      </c>
+      <c r="D17" t="n">
+        <v>23163</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JESUS GUSTAVO MARQUEZ GONZALEZ</t>
+          <t>RICARDO ALFREDO ARANDA DOWLING</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14-09-2026 15:17:57</t>
+          <t>01-10-2026 18:07:45</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1557,28 +1543,24 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>499</v>
-      </c>
-      <c r="M17" t="n">
-        <v>11</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>09-09-2027 15:17:57</t>
-        </is>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>76787</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1586,32 +1568,32 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>112237</v>
+        <v>112363</v>
       </c>
       <c r="C18" t="n">
-        <v>387278</v>
+        <v>344891</v>
       </c>
       <c r="D18" t="n">
-        <v>29435</v>
+        <v>22708</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ANA ABIGAIL GUILLEN ENRIQUEZ</t>
+          <t>DAVID CARLOS GALLARDO CONTRERAS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01-10-2026 7:46:21</t>
+          <t>03-10-2026 8:50:39</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1624,18 +1606,18 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>549</v>
+        <v>699</v>
       </c>
       <c r="M18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>26-09-2027 7:46:21</t>
+          <t>01-04-2027 8:50:39</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1643,7 +1625,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>106911</v>
+      </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1651,27 +1635,27 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>112322</v>
+        <v>112368</v>
       </c>
       <c r="C19" t="n">
-        <v>387986</v>
+        <v>387963</v>
       </c>
       <c r="D19" t="n">
-        <v>30143</v>
+        <v>30120</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MANUELA DE JESUS RUIZ ALUCANO</t>
+          <t>GIOVANNI ANTONIO VAZQUEZ RANGEL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>02-10-2026 13:00:38</t>
+          <t>02-10-2026 10:27:39</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1693,19 +1677,17 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>549</v>
-      </c>
-      <c r="M19" t="n">
-        <v>11</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>27-09-2027 13:00:38</t>
-        </is>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -1716,32 +1698,32 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>112278</v>
+        <v>110250</v>
       </c>
       <c r="C20" t="n">
-        <v>387863</v>
+        <v>347993</v>
       </c>
       <c r="D20" t="n">
-        <v>30020</v>
+        <v>90158</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FERNANDO  MANRIQUE MELLADO</t>
+          <t>VALERY MARISA HERNANDEZ  CASTILLO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01-10-2026 17:43:45</t>
+          <t>04-09-2026 16:33:31</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1754,24 +1736,28 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>549</v>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>30-08-2027 16:33:31</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>95723</v>
+      </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1779,32 +1765,32 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>112335</v>
+        <v>110251</v>
       </c>
       <c r="C21" t="n">
-        <v>388021</v>
+        <v>347990</v>
       </c>
       <c r="D21" t="n">
-        <v>30178</v>
+        <v>90155</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ANGELICA MARIA GRANADOS SANCHEZ</t>
+          <t>LUIS ARTURO  HERNANDEZ  SALGADO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>02-10-2026 17:22:05</t>
+          <t>04-09-2026 16:36:08</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1817,18 +1803,18 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>599</v>
+        <v>549</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>31-03-2027 17:22:05</t>
+          <t>30-08-2027 16:36:08</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1836,7 +1822,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>95721</v>
+      </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1844,29 +1832,29 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>110106</v>
+        <v>112274</v>
       </c>
       <c r="C22" t="n">
-        <v>204657</v>
+        <v>111039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>02165</t>
+          <t>08776</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ERANDI LIZBETH CRUZ  CASTILLO</t>
+          <t>PEDRO MARIO  VALENZUELA  PINTO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>AZAHARES CUL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>02-09-2026 13:25:36</t>
+          <t>01-10-2026 17:03:49</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1884,28 +1872,24 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>399</v>
-      </c>
-      <c r="M22" t="n">
-        <v>11</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>28-08-2027 13:25:36</t>
-        </is>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>7977</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1913,32 +1897,32 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>112263</v>
+        <v>112352</v>
       </c>
       <c r="C23" t="n">
-        <v>387820</v>
+        <v>388094</v>
       </c>
       <c r="D23" t="n">
-        <v>29977</v>
+        <v>30251</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RICARDO RAMIREZ  MARTINEZ</t>
+          <t>MIRIAM SELENE GARCIA POYORENA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>01-10-2026 15:26:38</t>
+          <t>02-10-2026 20:37:21</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1962,7 +1946,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>30-03-2027 15:26:38</t>
+          <t>31-03-2027 20:37:21</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1978,32 +1962,32 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>112299</v>
+        <v>112342</v>
       </c>
       <c r="C24" t="n">
-        <v>387908</v>
+        <v>388034</v>
       </c>
       <c r="D24" t="n">
-        <v>30065</v>
+        <v>30191</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ERIKA NATCHA MARTINEZ ANTONIO</t>
+          <t>RICARDO NOE  ZUÑIGA  PALACIOS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>01-10-2026 19:28:17</t>
+          <t>02-10-2026 17:49:53</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -2020,14 +2004,14 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>599</v>
+        <v>649</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>30-03-2027 19:28:17</t>
+          <t>27-09-2027 17:49:53</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2043,32 +2027,32 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>112343</v>
+        <v>112244</v>
       </c>
       <c r="C25" t="n">
-        <v>388038</v>
+        <v>157095</v>
       </c>
       <c r="D25" t="n">
-        <v>30195</v>
+        <v>54639</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ABRIL  HURTADO  PICHARDO</t>
+          <t>MARIA DE LOURDES ALVARES PADILLA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>02-10-2026 17:52:26</t>
+          <t>01-10-2026 10:15:02</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>30-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2081,18 +2065,18 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>599</v>
+        <v>399</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>31-03-2027 17:52:26</t>
+          <t>26-09-2027 10:15:02</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2100,7 +2084,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>4233</v>
+      </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2108,27 +2094,27 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>112300</v>
+        <v>112251</v>
       </c>
       <c r="C26" t="n">
-        <v>387867</v>
+        <v>387791</v>
       </c>
       <c r="D26" t="n">
-        <v>30024</v>
+        <v>29948</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GUADALUPE GEORGINA  GONZALEZ CIRIGO</t>
+          <t>ANGEL GABRIEL RIVERA SALAZAR</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>01-10-2026 19:36:27</t>
+          <t>01-10-2026 12:36:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2150,14 +2136,14 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>649</v>
+        <v>849</v>
       </c>
       <c r="M26" t="n">
         <v>11</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>26-09-2027 19:36:27</t>
+          <t>26-09-2027 12:36:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2173,32 +2159,32 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>112351</v>
+        <v>112319</v>
       </c>
       <c r="C27" t="n">
-        <v>179739</v>
+        <v>387974</v>
       </c>
       <c r="D27" t="n">
-        <v>77246</v>
+        <v>30131</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MARIA DE LA LUZ MARTINEZ ROMERO</t>
+          <t>UZIEL PICON  SOLIS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>02-10-2026 19:44:47</t>
+          <t>02-10-2026 11:58:57</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>02-01-2027 23:59:59</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2211,18 +2197,18 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>699</v>
+        <v>1549</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>31-03-2027 19:44:47</t>
+          <t>27-09-2027 11:58:57</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2230,9 +2216,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P27" t="n">
-        <v>32522</v>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2240,32 +2224,32 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>112187</v>
+        <v>112362</v>
       </c>
       <c r="C28" t="n">
-        <v>164685</v>
+        <v>383624</v>
       </c>
       <c r="D28" t="n">
-        <v>62218</v>
+        <v>25781</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OSCAR EDCARDA GUZMAN GONZALEZ</t>
+          <t>DAYSI GUADALUPE SANTACRUZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>30-09-2026 15:16:45</t>
+          <t>03-10-2026 8:45:37</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2278,26 +2262,26 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>549</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M28" t="n">
+        <v>5</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>01-04-2027 8:45:37</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>102910</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2305,32 +2289,32 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>112298</v>
+        <v>110240</v>
       </c>
       <c r="C29" t="n">
-        <v>387453</v>
+        <v>90728</v>
       </c>
       <c r="D29" t="n">
-        <v>29610</v>
+        <v>88499</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MARCELA GOMEZ DEANDAR</t>
+          <t>VALERIA V PEREZ VALDEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>PABELLON RTO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>01-10-2026 19:27:30</t>
+          <t>04-09-2026 9:56:12</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2343,26 +2327,26 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>849</v>
-      </c>
-      <c r="M29" t="n">
-        <v>11</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>26-09-2027 19:27:30</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>107840</v>
+      </c>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2370,27 +2354,27 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>112239</v>
+        <v>108953</v>
       </c>
       <c r="C30" t="n">
-        <v>387765</v>
+        <v>379812</v>
       </c>
       <c r="D30" t="n">
-        <v>29922</v>
+        <v>21970</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GABRIELA NICOLE INZUNZA VILLARREAL</t>
+          <t>VICTOR  CORTINAS  FAVELA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>01-10-2026 9:06:03</t>
+          <t>18-08-2026 17:37:56</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2408,18 +2392,18 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>999</v>
+        <v>849</v>
       </c>
       <c r="M30" t="n">
         <v>11</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>26-09-2027 9:06:03</t>
+          <t>13-08-2027 17:37:56</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2435,29 +2419,27 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>112256</v>
+        <v>112232</v>
       </c>
       <c r="C31" t="n">
-        <v>106839</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>04582</t>
-        </is>
+        <v>262903</v>
+      </c>
+      <c r="D31" t="n">
+        <v>60407</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>JAVIER SAUCEDO GUERRERO</t>
+          <t>RAUL  ZUÑIGA MARTINEZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>01-10-2026 13:31:57</t>
+          <t>01-10-2026 5:44:16</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2475,28 +2457,24 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>699</v>
-      </c>
-      <c r="M31" t="n">
-        <v>5</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>30-03-2027 13:31:57</t>
-        </is>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>82349</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2504,27 +2482,27 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>112288</v>
+        <v>112246</v>
       </c>
       <c r="C32" t="n">
-        <v>387884</v>
+        <v>386941</v>
       </c>
       <c r="D32" t="n">
-        <v>30041</v>
+        <v>29098</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DULCE MARIA  SERRANO  JUAREZ</t>
+          <t>FABIOLA  PLAZA  CARMONA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>01-10-2026 18:41:11</t>
+          <t>01-10-2026 11:04:12</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2546,14 +2524,14 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>699</v>
+        <v>849</v>
       </c>
       <c r="M32" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>30-03-2027 18:41:11</t>
+          <t>26-09-2027 11:04:12</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2569,34 +2547,32 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>112305</v>
+        <v>112296</v>
       </c>
       <c r="C33" t="n">
-        <v>211527</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>09035</t>
-        </is>
+        <v>387909</v>
+      </c>
+      <c r="D33" t="n">
+        <v>30066</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ALAN GEOVANNI RAMOS  FLORES</t>
+          <t>CESAR JOSUE  ROJO  OSORIO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SAN ISIDRO CUL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>02-10-2026 6:28:46</t>
+          <t>01-10-2026 19:22:26</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2613,19 +2589,17 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>599</v>
-      </c>
-      <c r="M33" t="n">
-        <v>5</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>31-03-2027 6:28:46</t>
-        </is>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -2636,27 +2610,27 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>112303</v>
+        <v>112331</v>
       </c>
       <c r="C34" t="n">
-        <v>222817</v>
+        <v>163266</v>
       </c>
       <c r="D34" t="n">
-        <v>20324</v>
+        <v>60799</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FRANCISCO  ROCHA LOPEZ</t>
+          <t>FERNANDO DAVID HERNANDEZ RAMIREZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>02-10-2026 5:28:54</t>
+          <t>02-10-2026 17:07:05</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2678,17 +2652,19 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>699</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>27-09-2027 17:07:05</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -2699,34 +2675,32 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>112317</v>
+        <v>112261</v>
       </c>
       <c r="C35" t="n">
-        <v>362544</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>04704</t>
-        </is>
+        <v>387404</v>
+      </c>
+      <c r="D35" t="n">
+        <v>29561</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DARIO ABRAM  GARCIA  REYNADA</t>
+          <t>CELENE VILLANUEVA  BRIONES</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>02-10-2026 11:20:56</t>
+          <t>01-10-2026 14:57:54</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>16-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2739,28 +2713,24 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>649</v>
-      </c>
-      <c r="M35" t="n">
-        <v>11</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>27-09-2027 11:20:56</t>
-        </is>
-      </c>
+        <v>949</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>101529</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2768,32 +2738,32 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>112367</v>
+        <v>112295</v>
       </c>
       <c r="C36" t="n">
-        <v>142180</v>
+        <v>347831</v>
       </c>
       <c r="D36" t="n">
-        <v>39798</v>
+        <v>89996</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KENIA GUADALUPE SILVA MEDINA</t>
+          <t>CARLOS ALBERTO LOPEZ ALARCON</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>03-10-2026 10:51:07</t>
+          <t>01-10-2026 19:21:26</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>12-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2810,21 +2780,23 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>399</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+        <v>699</v>
+      </c>
+      <c r="M36" t="n">
+        <v>5</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>30-03-2027 19:21:26</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>81999</v>
+        <v>95613</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
@@ -2833,27 +2805,27 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>112232</v>
+        <v>112239</v>
       </c>
       <c r="C37" t="n">
-        <v>262903</v>
+        <v>387765</v>
       </c>
       <c r="D37" t="n">
-        <v>60407</v>
+        <v>29922</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAUL  ZUÑIGA MARTINEZ</t>
+          <t>GABRIELA NICOLE INZUNZA VILLARREAL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>01-10-2026 5:44:16</t>
+          <t>01-10-2026 9:06:03</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2875,17 +2847,19 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>549</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+        <v>999</v>
+      </c>
+      <c r="M37" t="n">
+        <v>11</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>26-09-2027 9:06:03</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -2896,27 +2870,29 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>112246</v>
+        <v>112256</v>
       </c>
       <c r="C38" t="n">
-        <v>386941</v>
-      </c>
-      <c r="D38" t="n">
-        <v>29098</v>
+        <v>106839</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>04582</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FABIOLA  PLAZA  CARMONA</t>
+          <t>JAVIER SAUCEDO GUERRERO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>01-10-2026 11:04:12</t>
+          <t>01-10-2026 13:31:57</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2934,18 +2910,18 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>849</v>
+        <v>699</v>
       </c>
       <c r="M38" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>26-09-2027 11:04:12</t>
+          <t>30-03-2027 13:31:57</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2953,7 +2929,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>82349</v>
+      </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2961,27 +2939,27 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>112296</v>
+        <v>112288</v>
       </c>
       <c r="C39" t="n">
-        <v>387909</v>
+        <v>387884</v>
       </c>
       <c r="D39" t="n">
-        <v>30066</v>
+        <v>30041</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CESAR JOSUE  ROJO  OSORIO</t>
+          <t>DULCE MARIA  SERRANO  JUAREZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SAN ISIDRO CUL</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>01-10-2026 19:22:26</t>
+          <t>01-10-2026 18:41:11</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3005,15 +2983,17 @@
       <c r="L39" t="n">
         <v>699</v>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>5</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>30-03-2027 18:41:11</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -3024,27 +3004,29 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>112331</v>
+        <v>112305</v>
       </c>
       <c r="C40" t="n">
-        <v>163266</v>
-      </c>
-      <c r="D40" t="n">
-        <v>60799</v>
+        <v>211527</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>09035</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FERNANDO DAVID HERNANDEZ RAMIREZ</t>
+          <t>ALAN GEOVANNI RAMOS  FLORES</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>02-10-2026 17:07:05</t>
+          <t>02-10-2026 6:28:46</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3066,14 +3048,14 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>549</v>
+        <v>599</v>
       </c>
       <c r="M40" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>27-09-2027 17:07:05</t>
+          <t>31-03-2027 6:28:46</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3089,27 +3071,27 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>112243</v>
+        <v>110100</v>
       </c>
       <c r="C41" t="n">
-        <v>118726</v>
+        <v>289981</v>
       </c>
       <c r="D41" t="n">
-        <v>16436</v>
+        <v>87479</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>JONATHAN BERNAL REYNA</t>
+          <t>RICARDO HERNANDEZ CASTILLO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>STA CATARINA</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>01-10-2026 9:47:38</t>
+          <t>02-09-2026 10:19:32</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3127,18 +3109,18 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>599</v>
+        <v>499</v>
       </c>
       <c r="M41" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>30-03-2027 9:47:38</t>
+          <t>28-08-2027 10:19:32</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3146,7 +3128,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>107633</v>
+      </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -3154,27 +3138,27 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>112261</v>
+        <v>111587</v>
       </c>
       <c r="C42" t="n">
-        <v>387404</v>
+        <v>339078</v>
       </c>
       <c r="D42" t="n">
-        <v>29561</v>
+        <v>16896</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CELENE VILLANUEVA  BRIONES</t>
+          <t>PEDRO  MORALEZ  ESPARZA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>01-10-2026 14:57:54</t>
+          <t>22-09-2026 18:35:31</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3192,24 +3176,28 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>949</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+        <v>649</v>
+      </c>
+      <c r="M42" t="n">
+        <v>11</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>17-09-2027 18:35:31</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>91215</v>
+      </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -3217,27 +3205,29 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>112295</v>
+        <v>112289</v>
       </c>
       <c r="C43" t="n">
-        <v>347831</v>
-      </c>
-      <c r="D43" t="n">
-        <v>89996</v>
+        <v>9780</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>08709</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO LOPEZ ALARCON</t>
+          <t>CONSUELO MUÑOZ ROSALES</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>01-10-2026 19:21:26</t>
+          <t>01-10-2026 18:43:56</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3255,18 +3245,18 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>699</v>
+        <v>999</v>
       </c>
       <c r="M43" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>30-03-2027 19:21:26</t>
+          <t>26-09-2027 18:43:56</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3274,9 +3264,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P43" t="n">
-        <v>95613</v>
-      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -3284,32 +3272,32 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>112276</v>
+        <v>112323</v>
       </c>
       <c r="C44" t="n">
-        <v>90016</v>
+        <v>382611</v>
       </c>
       <c r="D44" t="n">
-        <v>87793</v>
+        <v>24768</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FRANCISCO GONZALEZ CHARLES</t>
+          <t>ALMA ANGELINA  GALVEZ  DOMINGUEZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>01-10-2026 17:27:02</t>
+          <t>02-10-2026 13:02:32</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3322,26 +3310,26 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>549</v>
-      </c>
-      <c r="M44" t="n">
-        <v>11</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>26-09-2027 17:27:02</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>110182</v>
+      </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3349,32 +3337,32 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>112326</v>
+        <v>112243</v>
       </c>
       <c r="C45" t="n">
-        <v>229384</v>
+        <v>118726</v>
       </c>
       <c r="D45" t="n">
-        <v>26889</v>
+        <v>16436</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>JOSE MIGUEL  MOSQUEDA MONTIEL</t>
+          <t>JONATHAN BERNAL REYNA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>02-10-2026 13:50:00</t>
+          <t>01-10-2026 9:47:38</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -3398,7 +3386,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>31-03-2027 13:50:00</t>
+          <t>30-03-2027 9:47:38</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3414,32 +3402,32 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>110100</v>
+        <v>112375</v>
       </c>
       <c r="C46" t="n">
-        <v>289981</v>
+        <v>388178</v>
       </c>
       <c r="D46" t="n">
-        <v>87479</v>
+        <v>30335</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RICARDO HERNANDEZ CASTILLO</t>
+          <t>MARTHA INES  VAZQUEZ IBARRA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>02-09-2026 10:19:32</t>
+          <t>03-10-2026 13:28:59</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3452,18 +3440,18 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>499</v>
+        <v>849</v>
       </c>
       <c r="M46" t="n">
         <v>11</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>28-08-2027 10:19:32</t>
+          <t>28-09-2027 13:28:59</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3471,9 +3459,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P46" t="n">
-        <v>107633</v>
-      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -3481,32 +3467,32 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>111587</v>
+        <v>112303</v>
       </c>
       <c r="C47" t="n">
-        <v>339078</v>
+        <v>222817</v>
       </c>
       <c r="D47" t="n">
-        <v>16896</v>
+        <v>20324</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PEDRO  MORALEZ  ESPARZA</t>
+          <t>FRANCISCO  ROCHA LOPEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>22-09-2026 18:35:31</t>
+          <t>02-10-2026 5:28:54</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3519,28 +3505,24 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>649</v>
-      </c>
-      <c r="M47" t="n">
-        <v>11</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>17-09-2027 18:35:31</t>
-        </is>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P47" t="n">
-        <v>91215</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3548,34 +3530,34 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>112289</v>
+        <v>112317</v>
       </c>
       <c r="C48" t="n">
-        <v>9780</v>
+        <v>362544</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>08709</t>
+          <t>04704</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CONSUELO MUÑOZ ROSALES</t>
+          <t>DARIO ABRAM  GARCIA  REYNADA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>01-10-2026 18:43:56</t>
+          <t>02-10-2026 11:20:56</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>16-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -3588,18 +3570,18 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>999</v>
+        <v>649</v>
       </c>
       <c r="M48" t="n">
         <v>11</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>26-09-2027 18:43:56</t>
+          <t>27-09-2027 11:20:56</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3607,7 +3589,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>101529</v>
+      </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -3615,32 +3599,32 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>112323</v>
+        <v>112367</v>
       </c>
       <c r="C49" t="n">
-        <v>382611</v>
+        <v>142180</v>
       </c>
       <c r="D49" t="n">
-        <v>24768</v>
+        <v>39798</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ALMA ANGELINA  GALVEZ  DOMINGUEZ</t>
+          <t>KENIA GUADALUPE SILVA MEDINA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>02-10-2026 13:02:32</t>
+          <t>03-10-2026 10:51:07</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>12-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3657,7 +3641,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>649</v>
+        <v>399</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3671,7 +3655,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>110182</v>
+        <v>81999</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
@@ -3680,27 +3664,27 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>112265</v>
+        <v>112276</v>
       </c>
       <c r="C50" t="n">
-        <v>387835</v>
+        <v>90016</v>
       </c>
       <c r="D50" t="n">
-        <v>29992</v>
+        <v>87793</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>VICTOR MARCELO CORTINAS FLORES</t>
+          <t>FRANCISCO GONZALEZ CHARLES</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>01-10-2026 16:15:24</t>
+          <t>01-10-2026 17:27:02</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3722,14 +3706,14 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>849</v>
+        <v>549</v>
       </c>
       <c r="M50" t="n">
         <v>11</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>26-09-2027 16:15:24</t>
+          <t>26-09-2027 17:27:02</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3745,27 +3729,27 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>112312</v>
+        <v>112326</v>
       </c>
       <c r="C51" t="n">
-        <v>156642</v>
+        <v>229384</v>
       </c>
       <c r="D51" t="n">
-        <v>54186</v>
+        <v>26889</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MARIA DEL ROCIO  RODRIGUEZ  FELIX</t>
+          <t>JOSE MIGUEL  MOSQUEDA MONTIEL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AZAHARES CUL</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>02-10-2026 10:15:11</t>
+          <t>02-10-2026 13:50:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3787,17 +3771,19 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>699</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M51" t="n">
+        <v>5</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>31-03-2027 13:50:00</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -3808,32 +3794,32 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>112365</v>
+        <v>112265</v>
       </c>
       <c r="C52" t="n">
-        <v>388131</v>
+        <v>387835</v>
       </c>
       <c r="D52" t="n">
-        <v>30288</v>
+        <v>29992</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SERGIO  RODRIGUEZ GARCIA</t>
+          <t>VICTOR MARCELO CORTINAS FLORES</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>03-10-2026 9:34:15</t>
+          <t>01-10-2026 16:15:24</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3850,14 +3836,14 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>549</v>
+        <v>849</v>
       </c>
       <c r="M52" t="n">
         <v>11</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>28-09-2027 9:34:15</t>
+          <t>26-09-2027 16:15:24</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3873,32 +3859,32 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>112273</v>
+        <v>112312</v>
       </c>
       <c r="C53" t="n">
-        <v>387843</v>
+        <v>156642</v>
       </c>
       <c r="D53" t="n">
-        <v>30000</v>
+        <v>54186</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GUADALUPE JAVIER CHAPA  HERRERA</t>
+          <t>MARIA DEL ROCIO  RODRIGUEZ  FELIX</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>AZAHARES CUL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>01-10-2026 17:02:04</t>
+          <t>02-10-2026 10:15:11</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3915,7 +3901,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>949</v>
+        <v>699</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -3936,32 +3922,32 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>112346</v>
+        <v>112365</v>
       </c>
       <c r="C54" t="n">
-        <v>22960</v>
+        <v>388131</v>
       </c>
       <c r="D54" t="n">
-        <v>21854</v>
+        <v>30288</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ANABEL  VALDENEGRO  MEJIA</t>
+          <t>SERGIO  RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>02-10-2026 18:24:47</t>
+          <t>03-10-2026 9:34:15</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3978,14 +3964,14 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>599</v>
+        <v>549</v>
       </c>
       <c r="M54" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>31-03-2027 18:24:47</t>
+          <t>28-09-2027 9:34:15</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4001,32 +3987,34 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>110273</v>
+        <v>112379</v>
       </c>
       <c r="C55" t="n">
-        <v>331811</v>
-      </c>
-      <c r="D55" t="n">
-        <v>16615</v>
+        <v>366299</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>08459</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LUIS EDUARDO BENITEZ BATHEN</t>
+          <t>KEILA NOHEMI CRUZ  GONZALEZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>05-09-2026 10:22:27</t>
+          <t>03-10-2026 14:26:06</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>04-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -4043,14 +4031,14 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>649</v>
+        <v>699</v>
       </c>
       <c r="M55" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>31-08-2027 10:22:27</t>
+          <t>01-04-2027 14:26:06</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4059,7 +4047,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>85520</v>
+        <v>102874</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
@@ -4068,27 +4056,29 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>112268</v>
+        <v>110106</v>
       </c>
       <c r="C56" t="n">
-        <v>387603</v>
-      </c>
-      <c r="D56" t="n">
-        <v>29760</v>
+        <v>204657</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>02165</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ALEXIS TERRAZA VALENZUELA</t>
+          <t>ERANDI LIZBETH CRUZ  CASTILLO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>01-10-2026 16:52:36</t>
+          <t>02-09-2026 13:25:36</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4106,18 +4096,18 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>599</v>
+        <v>399</v>
       </c>
       <c r="M56" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>30-03-2027 16:52:36</t>
+          <t>28-08-2027 13:25:36</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4125,7 +4115,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>7977</v>
+      </c>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -4133,32 +4125,32 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>112359</v>
+        <v>112263</v>
       </c>
       <c r="C57" t="n">
-        <v>388112</v>
+        <v>387820</v>
       </c>
       <c r="D57" t="n">
-        <v>30269</v>
+        <v>29977</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>JENNIFER EHUNICE CAMACHO VARO</t>
+          <t>RICARDO RAMIREZ  MARTINEZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>03-10-2026 7:32:36</t>
+          <t>01-10-2026 15:26:38</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -4182,7 +4174,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>01-04-2027 7:32:36</t>
+          <t>30-03-2027 15:26:38</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4198,27 +4190,27 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>112248</v>
+        <v>112299</v>
       </c>
       <c r="C58" t="n">
-        <v>67098</v>
+        <v>387908</v>
       </c>
       <c r="D58" t="n">
-        <v>64929</v>
+        <v>30065</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JARI BLANCARTE CASTRO</t>
+          <t>ERIKA NATCHA MARTINEZ ANTONIO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>01-10-2026 11:45:13</t>
+          <t>01-10-2026 19:28:17</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4236,7 +4228,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>CANCELADO</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -4247,7 +4239,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>30-03-2027 11:45:13</t>
+          <t>30-03-2027 19:28:17</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4263,32 +4255,32 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>112279</v>
+        <v>112300</v>
       </c>
       <c r="C59" t="n">
-        <v>277374</v>
+        <v>387867</v>
       </c>
       <c r="D59" t="n">
-        <v>74875</v>
+        <v>30024</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MARIA ISABEL SOJO REYNAGA</t>
+          <t>GUADALUPE GEORGINA  GONZALEZ CIRIGO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>01-10-2026 17:59:41</t>
+          <t>01-10-2026 19:36:27</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>04-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -4305,14 +4297,14 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M59" t="n">
         <v>11</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>26-09-2027 17:59:41</t>
+          <t>26-09-2027 19:36:27</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4328,27 +4320,29 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>112253</v>
+        <v>110818</v>
       </c>
       <c r="C60" t="n">
-        <v>387797</v>
-      </c>
-      <c r="D60" t="n">
-        <v>29954</v>
+        <v>312013</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>09512</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>JOSHA JANDRY  BELLO  GONZALEZ</t>
+          <t>JESUS GUSTAVO MARQUEZ GONZALEZ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>01-10-2026 13:06:16</t>
+          <t>14-09-2026 15:17:57</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4366,18 +4360,18 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>649</v>
+        <v>499</v>
       </c>
       <c r="M60" t="n">
         <v>11</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>26-09-2027 13:06:16</t>
+          <t>09-09-2027 15:17:57</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4385,7 +4379,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>76787</v>
+      </c>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -4393,27 +4389,27 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>112292</v>
+        <v>112237</v>
       </c>
       <c r="C61" t="n">
-        <v>386711</v>
+        <v>387278</v>
       </c>
       <c r="D61" t="n">
-        <v>28868</v>
+        <v>29435</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ANA DELIA  LOPEZ  NIEBLAS</t>
+          <t>ANA ABIGAIL GUILLEN ENRIQUEZ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>01-10-2026 19:10:21</t>
+          <t>01-10-2026 7:46:21</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4435,14 +4431,14 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>599</v>
+        <v>549</v>
       </c>
       <c r="M61" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>30-03-2027 19:10:21</t>
+          <t>26-09-2027 7:46:21</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4458,27 +4454,27 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>112310</v>
+        <v>112322</v>
       </c>
       <c r="C62" t="n">
-        <v>387950</v>
+        <v>387986</v>
       </c>
       <c r="D62" t="n">
-        <v>30107</v>
+        <v>30143</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GABRIEL TREJO CAMACHO</t>
+          <t>MANUELA DE JESUS RUIZ ALUCANO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>02-10-2026 8:42:40</t>
+          <t>02-10-2026 13:00:38</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4500,14 +4496,14 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>849</v>
+        <v>549</v>
       </c>
       <c r="M62" t="n">
         <v>11</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>27-09-2027 8:42:40</t>
+          <t>27-09-2027 13:00:38</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4523,32 +4519,32 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>112332</v>
+        <v>112187</v>
       </c>
       <c r="C63" t="n">
-        <v>388016</v>
+        <v>164685</v>
       </c>
       <c r="D63" t="n">
-        <v>30173</v>
+        <v>62218</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>JOSE IGNACIO  AGUIRRE  HERNANDEZ</t>
+          <t>OSCAR EDCARDA GUZMAN GONZALEZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>02-10-2026 17:08:40</t>
+          <t>30-09-2026 15:16:45</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -4561,26 +4557,26 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L63" t="n">
         <v>549</v>
       </c>
-      <c r="M63" t="n">
-        <v>11</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>27-09-2027 17:08:40</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>102910</v>
+      </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -4588,32 +4584,32 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>112364</v>
+        <v>112372</v>
       </c>
       <c r="C64" t="n">
-        <v>215600</v>
+        <v>388143</v>
       </c>
       <c r="D64" t="n">
-        <v>13108</v>
+        <v>30300</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>VERONICA LUCIA ALVAREZ ZAVALA</t>
+          <t>JORDAN GUILLERMO CABALLERO PEÑA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>03-10-2026 9:02:37</t>
+          <t>03-10-2026 13:03:25</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>04-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -4626,18 +4622,18 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>699</v>
+        <v>849</v>
       </c>
       <c r="M64" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>01-04-2027 9:02:37</t>
+          <t>28-09-2027 13:03:25</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4645,9 +4641,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P64" t="n">
-        <v>54458</v>
-      </c>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -4655,29 +4649,27 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>110103</v>
+        <v>112343</v>
       </c>
       <c r="C65" t="n">
-        <v>202835</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>00343</t>
-        </is>
+        <v>388038</v>
+      </c>
+      <c r="D65" t="n">
+        <v>30195</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CRISTOBAL TIRADO CASTAÑEDA</t>
+          <t>ABRIL  HURTADO  PICHARDO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>02-09-2026 11:12:05</t>
+          <t>02-10-2026 17:52:26</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4695,18 +4687,18 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>499</v>
+        <v>599</v>
       </c>
       <c r="M65" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>28-08-2027 11:12:05</t>
+          <t>31-03-2027 17:52:26</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -4714,9 +4706,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P65" t="n">
-        <v>91359</v>
-      </c>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -4724,32 +4714,32 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>112270</v>
+        <v>112377</v>
       </c>
       <c r="C66" t="n">
-        <v>385596</v>
+        <v>331792</v>
       </c>
       <c r="D66" t="n">
-        <v>27753</v>
+        <v>16596</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>LUIS GIOVANNIE GARCIA  HERNADEZ</t>
+          <t>CINTHIA LIZETH  GONZALEZ  GALLEGOS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>01-10-2026 16:55:45</t>
+          <t>03-10-2026 13:51:36</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01-01-2027 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4766,14 +4756,14 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1549</v>
+        <v>599</v>
       </c>
       <c r="M66" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>26-09-2027 16:55:45</t>
+          <t>01-04-2027 13:51:36</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -4789,27 +4779,27 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>112293</v>
+        <v>112278</v>
       </c>
       <c r="C67" t="n">
-        <v>134981</v>
+        <v>387863</v>
       </c>
       <c r="D67" t="n">
-        <v>32629</v>
+        <v>30020</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA  RAMON  DE LA CRUZ</t>
+          <t>FERNANDO  MANRIQUE MELLADO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>01-10-2026 19:11:32</t>
+          <t>01-10-2026 17:43:45</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4831,19 +4821,17 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>599</v>
-      </c>
-      <c r="M67" t="n">
-        <v>5</v>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>30-03-2027 19:11:32</t>
-        </is>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
@@ -4854,32 +4842,32 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>112302</v>
+        <v>112335</v>
       </c>
       <c r="C68" t="n">
-        <v>351343</v>
+        <v>388021</v>
       </c>
       <c r="D68" t="n">
-        <v>93507</v>
+        <v>30178</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ASTRID ESTHEFANY ORGEN  OBESO</t>
+          <t>ANGELICA MARIA GRANADOS SANCHEZ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AZAHARES CUL</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>01-10-2026 20:10:26</t>
+          <t>02-10-2026 17:22:05</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -4903,7 +4891,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>30-03-2027 20:10:26</t>
+          <t>31-03-2027 17:22:05</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -4919,27 +4907,27 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>112336</v>
+        <v>112351</v>
       </c>
       <c r="C69" t="n">
-        <v>172829</v>
+        <v>179739</v>
       </c>
       <c r="D69" t="n">
-        <v>70348</v>
+        <v>77246</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>EVA ELIZABETH ARREOLA LOPEZ</t>
+          <t>MARIA DE LA LUZ MARTINEZ ROMERO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SEND CHIH</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>02-10-2026 17:24:08</t>
+          <t>02-10-2026 19:44:47</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4957,18 +4945,18 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>549</v>
+        <v>699</v>
       </c>
       <c r="M69" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>27-09-2027 17:24:08</t>
+          <t>31-03-2027 19:44:47</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -4976,7 +4964,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>32522</v>
+      </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -4984,32 +4974,32 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>110104</v>
+        <v>112298</v>
       </c>
       <c r="C70" t="n">
-        <v>129528</v>
+        <v>387453</v>
       </c>
       <c r="D70" t="n">
-        <v>27196</v>
+        <v>29610</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MARCO ANTONIO BARRAZA  PAREDES</t>
+          <t>MARCELA GOMEZ DEANDAR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SEND CHIH</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>02-09-2026 11:17:33</t>
+          <t>01-10-2026 19:27:30</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -5022,18 +5012,18 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>399</v>
+        <v>849</v>
       </c>
       <c r="M70" t="n">
         <v>11</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>28-08-2027 11:17:33</t>
+          <t>26-09-2027 19:27:30</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5041,9 +5031,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P70" t="n">
-        <v>66241</v>
-      </c>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -5051,34 +5039,32 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>111397</v>
+        <v>112346</v>
       </c>
       <c r="C71" t="n">
-        <v>361169</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>03334</t>
-        </is>
+        <v>22960</v>
+      </c>
+      <c r="D71" t="n">
+        <v>21854</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SONIA LOPEZ  RUIZ</t>
+          <t>ANABEL  VALDENEGRO  MEJIA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>21-09-2026 17:26:29</t>
+          <t>02-10-2026 18:24:47</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -5091,26 +5077,26 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>799</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M71" t="n">
+        <v>5</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>31-03-2027 18:24:47</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P71" t="n">
-        <v>100529</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -5118,27 +5104,27 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>112258</v>
+        <v>112268</v>
       </c>
       <c r="C72" t="n">
-        <v>350328</v>
+        <v>387603</v>
       </c>
       <c r="D72" t="n">
-        <v>92492</v>
+        <v>29760</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PAMELA RODRIGUEZ N</t>
+          <t>ALEXIS TERRAZA VALENZUELA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>01-10-2026 14:03:38</t>
+          <t>01-10-2026 16:52:36</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5160,14 +5146,14 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>649</v>
+        <v>599</v>
       </c>
       <c r="M72" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>26-09-2027 14:03:38</t>
+          <t>30-03-2027 16:52:36</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5183,32 +5169,32 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>112294</v>
+        <v>112359</v>
       </c>
       <c r="C73" t="n">
-        <v>387904</v>
+        <v>388112</v>
       </c>
       <c r="D73" t="n">
-        <v>30061</v>
+        <v>30269</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LAISHA AMAIRAMI DOMINGUEZ GARCIA</t>
+          <t>JENNIFER EHUNICE CAMACHO VARO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SAN ISIDRO CUL</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>01-10-2026 19:16:44</t>
+          <t>03-10-2026 7:32:36</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -5225,17 +5211,19 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>699</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M73" t="n">
+        <v>5</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>01-04-2027 7:32:36</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -5246,32 +5234,32 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>112337</v>
+        <v>112273</v>
       </c>
       <c r="C74" t="n">
-        <v>388027</v>
+        <v>387843</v>
       </c>
       <c r="D74" t="n">
-        <v>30184</v>
+        <v>30000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MARTHA KARINA LOPEZ  ALQUICIRA</t>
+          <t>GUADALUPE JAVIER CHAPA  HERRERA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>02-10-2026 17:30:59</t>
+          <t>01-10-2026 17:02:04</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>02-01-2027 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -5288,19 +5276,17 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1549</v>
-      </c>
-      <c r="M74" t="n">
-        <v>9</v>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>27-09-2027 17:30:59</t>
-        </is>
-      </c>
+        <v>949</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -5311,32 +5297,32 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>112238</v>
+        <v>112373</v>
       </c>
       <c r="C75" t="n">
-        <v>36177</v>
+        <v>297702</v>
       </c>
       <c r="D75" t="n">
-        <v>34091</v>
+        <v>95200</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>DENISSE  VARGAS MARTINEZZ</t>
+          <t>BRAYAN SANDOVAL DE LA CRUZ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>01-10-2026 8:10:41</t>
+          <t>03-10-2026 13:14:41</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -5353,21 +5339,23 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>599</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+        <v>699</v>
+      </c>
+      <c r="M75" t="n">
+        <v>5</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>01-04-2027 13:14:41</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>53295</v>
+        <v>68991</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
@@ -5376,32 +5364,32 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>112304</v>
+        <v>110268</v>
       </c>
       <c r="C76" t="n">
-        <v>387933</v>
+        <v>377331</v>
       </c>
       <c r="D76" t="n">
-        <v>30090</v>
+        <v>19490</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ALISON ORTEGA GOMEZ</t>
+          <t>JENNIFER HERNANDEZ SAN JUAN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>02-10-2026 6:15:03</t>
+          <t>05-09-2026 7:15:20</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>04-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -5414,26 +5402,26 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>549</v>
       </c>
-      <c r="M76" t="n">
-        <v>11</v>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>27-09-2027 6:15:03</t>
-        </is>
-      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>107931</v>
+      </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -5441,32 +5429,32 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>112340</v>
+        <v>110273</v>
       </c>
       <c r="C77" t="n">
-        <v>388031</v>
+        <v>331811</v>
       </c>
       <c r="D77" t="n">
-        <v>30188</v>
+        <v>16615</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>JOEL AURELIO  MEJIA  AGUILAR</t>
+          <t>LUIS EDUARDO BENITEZ BATHEN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>02-10-2026 17:39:50</t>
+          <t>05-09-2026 10:22:27</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>04-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -5479,18 +5467,18 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>599</v>
+        <v>649</v>
       </c>
       <c r="M77" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>31-03-2027 17:39:50</t>
+          <t>31-08-2027 10:22:27</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -5498,7 +5486,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr"/>
+      <c r="P77" t="n">
+        <v>85520</v>
+      </c>
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -5506,27 +5496,27 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>112280</v>
+        <v>112248</v>
       </c>
       <c r="C78" t="n">
-        <v>125817</v>
+        <v>67098</v>
       </c>
       <c r="D78" t="n">
-        <v>23492</v>
+        <v>64929</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ALEJANDRO  ARREDONDO BOJORQUEZ</t>
+          <t>JARI BLANCARTE CASTRO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>01-10-2026 18:03:34</t>
+          <t>01-10-2026 11:45:13</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5544,26 +5534,26 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>699</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M78" t="n">
+        <v>5</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>30-03-2027 11:45:13</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P78" t="n">
-        <v>43718</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
@@ -5571,34 +5561,32 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>112347</v>
+        <v>112279</v>
       </c>
       <c r="C79" t="n">
-        <v>104900</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>02647</t>
-        </is>
+        <v>277374</v>
+      </c>
+      <c r="D79" t="n">
+        <v>74875</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>JORGE VALENCIA CALDERON</t>
+          <t>MARIA ISABEL SOJO REYNAGA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>02-10-2026 18:35:24</t>
+          <t>01-10-2026 17:59:41</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>04-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -5611,18 +5599,18 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>699</v>
+        <v>549</v>
       </c>
       <c r="M79" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>31-03-2027 18:35:24</t>
+          <t>26-09-2027 17:59:41</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -5630,9 +5618,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P79" t="n">
-        <v>73428</v>
-      </c>
+      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
@@ -5640,32 +5626,32 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>112271</v>
+        <v>112349</v>
       </c>
       <c r="C80" t="n">
-        <v>387846</v>
+        <v>388071</v>
       </c>
       <c r="D80" t="n">
-        <v>30003</v>
+        <v>30228</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MARIA CRISTINA GARCIA GOMEZ</t>
+          <t>REYNA CRUZ HUERTAS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>01-10-2026 16:57:21</t>
+          <t>02-10-2026 19:07:17</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -5682,7 +5668,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>949</v>
+        <v>699</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -5703,32 +5689,32 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>112267</v>
+        <v>111023</v>
       </c>
       <c r="C81" t="n">
-        <v>339819</v>
+        <v>215153</v>
       </c>
       <c r="D81" t="n">
-        <v>17637</v>
+        <v>12661</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>TOBIAS FREIDTAINS FREIDTAINS</t>
+          <t>LUIS FERNANDO  CESEÑA VENEGAS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>01-10-2026 16:52:34</t>
+          <t>16-09-2026 10:13:11</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>04-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -5741,11 +5727,11 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>799</v>
+        <v>399</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -5758,7 +5744,9 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr"/>
+      <c r="P81" t="n">
+        <v>51091</v>
+      </c>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -5766,27 +5754,27 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>112328</v>
+        <v>112327</v>
       </c>
       <c r="C82" t="n">
-        <v>388010</v>
+        <v>387847</v>
       </c>
       <c r="D82" t="n">
-        <v>30167</v>
+        <v>30004</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>GENOVA  LEDESMA ZETINA</t>
+          <t>RAYMUNDO GARCIA FRAGOSO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>02-10-2026 16:39:59</t>
+          <t>02-10-2026 15:26:43</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5808,14 +5796,14 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>849</v>
+        <v>599</v>
       </c>
       <c r="M82" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>27-09-2027 16:39:59</t>
+          <t>31-03-2027 15:26:43</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -5831,17 +5819,17 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>112353</v>
+        <v>110235</v>
       </c>
       <c r="C83" t="n">
-        <v>93971</v>
+        <v>144872</v>
       </c>
       <c r="D83" t="n">
-        <v>91730</v>
+        <v>42466</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>GILBERTO ALEJANDRO VALENZUELA MEZA</t>
+          <t>ZAYRA RUBY BALCAZAR GONZALEZ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5851,12 +5839,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>02-10-2026 20:48:51</t>
+          <t>04-09-2026 8:19:38</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>04-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -5869,18 +5857,18 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>549</v>
+        <v>449</v>
       </c>
       <c r="M83" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>27-09-2027 20:48:51</t>
+          <t>03-03-2027 8:19:38</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -5888,7 +5876,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr"/>
+      <c r="P83" t="n">
+        <v>46172</v>
+      </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -5896,32 +5886,32 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>112360</v>
+        <v>112271</v>
       </c>
       <c r="C84" t="n">
-        <v>388114</v>
+        <v>387846</v>
       </c>
       <c r="D84" t="n">
-        <v>30271</v>
+        <v>30003</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LIZZY CARELI CAMACHO VARO</t>
+          <t>MARIA CRISTINA GARCIA GOMEZ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>03-10-2026 7:41:13</t>
+          <t>01-10-2026 16:57:21</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -5938,19 +5928,17 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>599</v>
-      </c>
-      <c r="M84" t="n">
-        <v>5</v>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>01-04-2027 7:41:13</t>
-        </is>
-      </c>
+        <v>949</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -5961,32 +5949,32 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>112349</v>
+        <v>112240</v>
       </c>
       <c r="C85" t="n">
-        <v>388071</v>
+        <v>326427</v>
       </c>
       <c r="D85" t="n">
-        <v>30228</v>
+        <v>23366</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>REYNA CRUZ HUERTAS</t>
+          <t>ANABEL GÓMEZ  RAMOS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>02-10-2026 19:07:17</t>
+          <t>01-10-2026 9:30:16</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -6003,17 +5991,19 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>699</v>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M85" t="n">
+        <v>5</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>30-03-2027 9:30:16</t>
+        </is>
+      </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P85" t="inlineStr"/>
@@ -6024,27 +6014,29 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>112241</v>
+        <v>112257</v>
       </c>
       <c r="C86" t="n">
-        <v>154646</v>
-      </c>
-      <c r="D86" t="n">
-        <v>52201</v>
+        <v>5992</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>04930</t>
+        </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DAVID EMILIANO  MALDONADO  VELASQUEZ</t>
+          <t>JAZMIN GUADALUPE ARELLANOS SAUCEDA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>AZAHARES CUL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>01-10-2026 9:34:09</t>
+          <t>01-10-2026 13:46:44</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6073,7 +6065,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>30-03-2027 9:34:09</t>
+          <t>30-03-2027 13:46:44</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -6089,27 +6081,27 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>112286</v>
+        <v>112287</v>
       </c>
       <c r="C87" t="n">
-        <v>387878</v>
+        <v>330617</v>
       </c>
       <c r="D87" t="n">
-        <v>30035</v>
+        <v>15671</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BRYAN ISRAEL GARCIA  GONZALEZ</t>
+          <t>RAMIRO MARTINEZ RAMIREZ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>01-10-2026 18:28:15</t>
+          <t>01-10-2026 18:35:12</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6133,15 +6125,17 @@
       <c r="L87" t="n">
         <v>549</v>
       </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+      <c r="M87" t="n">
+        <v>11</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>26-09-2027 18:35:12</t>
+        </is>
+      </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P87" t="inlineStr"/>
@@ -6152,32 +6146,32 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>112350</v>
+        <v>112338</v>
       </c>
       <c r="C88" t="n">
-        <v>388067</v>
+        <v>388028</v>
       </c>
       <c r="D88" t="n">
-        <v>30224</v>
+        <v>30185</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>GABRIEL  TELLEZ  CHANG</t>
+          <t>ANDREA  GALINDO  LOPEZ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>02-10-2026 19:11:38</t>
+          <t>02-10-2026 17:31:25</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>02-01-2027 23:59:59</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -6194,14 +6188,14 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>549</v>
+        <v>1549</v>
       </c>
       <c r="M88" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>27-09-2027 19:11:38</t>
+          <t>27-09-2027 17:31:25</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6217,32 +6211,32 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>112327</v>
+        <v>110112</v>
       </c>
       <c r="C89" t="n">
-        <v>387847</v>
+        <v>374211</v>
       </c>
       <c r="D89" t="n">
-        <v>30004</v>
+        <v>16371</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RAYMUNDO GARCIA FRAGOSO</t>
+          <t>ANA KAREN  QUEZADA  RAMIREZ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>02-10-2026 15:26:43</t>
+          <t>02-09-2026 15:52:16</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>17-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -6255,26 +6249,26 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L89" t="n">
         <v>599</v>
       </c>
-      <c r="M89" t="n">
-        <v>5</v>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>31-03-2027 15:26:43</t>
-        </is>
-      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>106345</v>
+      </c>
       <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
@@ -6282,32 +6276,32 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>112108</v>
+        <v>112241</v>
       </c>
       <c r="C90" t="n">
-        <v>171319</v>
+        <v>154646</v>
       </c>
       <c r="D90" t="n">
-        <v>68838</v>
+        <v>52201</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MARIA  DE JESUS CARDONA ALVARADO</t>
+          <t>DAVID EMILIANO  MALDONADO  VELASQUEZ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>29-09-2026 18:05:34</t>
+          <t>01-10-2026 9:34:09</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -6320,18 +6314,18 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>449</v>
+        <v>599</v>
       </c>
       <c r="M90" t="n">
         <v>5</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>28-03-2027 18:05:34</t>
+          <t>30-03-2027 9:34:09</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6339,9 +6333,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P90" t="n">
-        <v>77276</v>
-      </c>
+      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
@@ -6349,32 +6341,32 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>112333</v>
+        <v>112286</v>
       </c>
       <c r="C91" t="n">
-        <v>388019</v>
+        <v>387878</v>
       </c>
       <c r="D91" t="n">
-        <v>30176</v>
+        <v>30035</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>JESUS ALFREDO  SAUCEDO  HERNANDEZ</t>
+          <t>BRYAN ISRAEL GARCIA  GONZALEZ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>02-10-2026 17:11:11</t>
+          <t>01-10-2026 18:28:15</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -6393,17 +6385,15 @@
       <c r="L91" t="n">
         <v>549</v>
       </c>
-      <c r="M91" t="n">
-        <v>11</v>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>27-09-2027 17:11:11</t>
-        </is>
-      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P91" t="inlineStr"/>
@@ -6414,32 +6404,32 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>112240</v>
+        <v>112350</v>
       </c>
       <c r="C92" t="n">
-        <v>326427</v>
+        <v>388067</v>
       </c>
       <c r="D92" t="n">
-        <v>23366</v>
+        <v>30224</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ANABEL GÓMEZ  RAMOS</t>
+          <t>GABRIEL  TELLEZ  CHANG</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>STA CATARINA</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>01-10-2026 9:30:16</t>
+          <t>02-10-2026 19:11:38</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -6456,14 +6446,14 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>599</v>
+        <v>549</v>
       </c>
       <c r="M92" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>30-03-2027 9:30:16</t>
+          <t>27-09-2027 19:11:38</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -6479,29 +6469,27 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>112257</v>
+        <v>112267</v>
       </c>
       <c r="C93" t="n">
-        <v>5992</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>04930</t>
-        </is>
+        <v>339819</v>
+      </c>
+      <c r="D93" t="n">
+        <v>17637</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>JAZMIN GUADALUPE ARELLANOS SAUCEDA</t>
+          <t>TOBIAS FREIDTAINS FREIDTAINS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AZAHARES CUL</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>01-10-2026 13:46:44</t>
+          <t>01-10-2026 16:52:34</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6523,19 +6511,17 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>599</v>
-      </c>
-      <c r="M93" t="n">
-        <v>5</v>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>30-03-2027 13:46:44</t>
-        </is>
-      </c>
+        <v>799</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P93" t="inlineStr"/>
@@ -6546,32 +6532,32 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>112287</v>
+        <v>112328</v>
       </c>
       <c r="C94" t="n">
-        <v>330617</v>
+        <v>388010</v>
       </c>
       <c r="D94" t="n">
-        <v>15671</v>
+        <v>30167</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RAMIRO MARTINEZ RAMIREZ</t>
+          <t>GENOVA  LEDESMA ZETINA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>01-10-2026 18:35:12</t>
+          <t>02-10-2026 16:39:59</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -6588,14 +6574,14 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>549</v>
+        <v>849</v>
       </c>
       <c r="M94" t="n">
         <v>11</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>26-09-2027 18:35:12</t>
+          <t>27-09-2027 16:39:59</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -6611,32 +6597,32 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>112338</v>
+        <v>112353</v>
       </c>
       <c r="C95" t="n">
-        <v>388028</v>
+        <v>93971</v>
       </c>
       <c r="D95" t="n">
-        <v>30185</v>
+        <v>91730</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ANDREA  GALINDO  LOPEZ</t>
+          <t>GILBERTO ALEJANDRO VALENZUELA MEZA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>02-10-2026 17:31:25</t>
+          <t>02-10-2026 20:48:51</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>02-01-2027 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -6653,14 +6639,14 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1549</v>
+        <v>549</v>
       </c>
       <c r="M95" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>27-09-2027 17:31:25</t>
+          <t>27-09-2027 20:48:51</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -6676,32 +6662,32 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>111012</v>
+        <v>112360</v>
       </c>
       <c r="C96" t="n">
-        <v>68471</v>
+        <v>388114</v>
       </c>
       <c r="D96" t="n">
-        <v>66299</v>
+        <v>30271</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>JESUS MAURICIO VALTIERRA HERNANDEZ</t>
+          <t>LIZZY CARELI CAMACHO VARO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>15-09-2026 19:54:08</t>
+          <t>03-10-2026 7:41:13</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -6714,18 +6700,18 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>499</v>
+        <v>599</v>
       </c>
       <c r="M96" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>10-09-2027 19:54:08</t>
+          <t>01-04-2027 7:41:13</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -6733,9 +6719,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P96" t="n">
-        <v>102987</v>
-      </c>
+      <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
@@ -6743,27 +6727,27 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>112315</v>
+        <v>112108</v>
       </c>
       <c r="C97" t="n">
-        <v>387966</v>
+        <v>171319</v>
       </c>
       <c r="D97" t="n">
-        <v>30123</v>
+        <v>68838</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MAURICIO MACIAS SILLER</t>
+          <t>MARIA  DE JESUS CARDONA ALVARADO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>02-10-2026 10:56:58</t>
+          <t>29-09-2026 18:05:34</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6781,24 +6765,28 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>949</v>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+        <v>449</v>
+      </c>
+      <c r="M97" t="n">
+        <v>5</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>28-03-2027 18:05:34</t>
+        </is>
+      </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>77276</v>
+      </c>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
@@ -6806,27 +6794,27 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>112329</v>
+        <v>112333</v>
       </c>
       <c r="C98" t="n">
-        <v>388012</v>
+        <v>388019</v>
       </c>
       <c r="D98" t="n">
-        <v>30169</v>
+        <v>30176</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>JOSE LUIS  GARELLI LEDESMA</t>
+          <t>JESUS ALFREDO  SAUCEDO  HERNANDEZ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>02-10-2026 16:45:25</t>
+          <t>02-10-2026 17:11:11</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6848,14 +6836,14 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>849</v>
+        <v>549</v>
       </c>
       <c r="M98" t="n">
         <v>11</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>27-09-2027 16:45:25</t>
+          <t>27-09-2027 17:11:11</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -6871,32 +6859,32 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>112348</v>
+        <v>112376</v>
       </c>
       <c r="C99" t="n">
-        <v>241357</v>
+        <v>388180</v>
       </c>
       <c r="D99" t="n">
-        <v>38862</v>
+        <v>30337</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MARIA LUCERO PASTOR OLIVERA</t>
+          <t>ALEJANDRO DANIEL MARTINEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>02-10-2026 19:00:07</t>
+          <t>03-10-2026 13:36:21</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -6913,17 +6901,19 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>699</v>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+        <v>849</v>
+      </c>
+      <c r="M99" t="n">
+        <v>11</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>28-09-2027 13:36:21</t>
+        </is>
+      </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P99" t="inlineStr"/>
@@ -6934,27 +6924,27 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>112290</v>
+        <v>111012</v>
       </c>
       <c r="C100" t="n">
-        <v>387881</v>
+        <v>68471</v>
       </c>
       <c r="D100" t="n">
-        <v>30038</v>
+        <v>66299</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ALFREDO QUEZADA CURIEL</t>
+          <t>JESUS MAURICIO VALTIERRA HERNANDEZ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>01-10-2026 18:44:30</t>
+          <t>15-09-2026 19:54:08</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6972,18 +6962,18 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>999</v>
+        <v>499</v>
       </c>
       <c r="M100" t="n">
         <v>11</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>26-09-2027 18:44:30</t>
+          <t>10-09-2027 19:54:08</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -6991,7 +6981,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr"/>
+      <c r="P100" t="n">
+        <v>102987</v>
+      </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
@@ -6999,27 +6991,27 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>112307</v>
+        <v>112315</v>
       </c>
       <c r="C101" t="n">
-        <v>387513</v>
+        <v>387966</v>
       </c>
       <c r="D101" t="n">
-        <v>29670</v>
+        <v>30123</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>LIZETH RAMIREZ MARTINEZ</t>
+          <t>MAURICIO MACIAS SILLER</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>02-10-2026 7:13:03</t>
+          <t>02-10-2026 10:56:58</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7041,19 +7033,17 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>649</v>
-      </c>
-      <c r="M101" t="n">
-        <v>11</v>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>27-09-2027 7:13:03</t>
-        </is>
-      </c>
+        <v>949</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -7064,32 +7054,32 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>112339</v>
+        <v>112329</v>
       </c>
       <c r="C102" t="n">
-        <v>388032</v>
+        <v>388012</v>
       </c>
       <c r="D102" t="n">
-        <v>30189</v>
+        <v>30169</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ARACELI LOPEZ  ALQUICIRA</t>
+          <t>JOSE LUIS  GARELLI LEDESMA</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>02-10-2026 17:38:20</t>
+          <t>02-10-2026 16:45:25</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>02-01-2027 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -7106,17 +7096,19 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1549</v>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
+        <v>849</v>
+      </c>
+      <c r="M102" t="n">
+        <v>11</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>27-09-2027 16:45:25</t>
+        </is>
+      </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -7127,27 +7119,27 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>112354</v>
+        <v>112348</v>
       </c>
       <c r="C103" t="n">
-        <v>386175</v>
+        <v>241357</v>
       </c>
       <c r="D103" t="n">
-        <v>28332</v>
+        <v>38862</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>PAULINA DEL CARMEN SANCHEZ CRUZ</t>
+          <t>MARIA LUCERO PASTOR OLIVERA</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>02-10-2026 22:01:09</t>
+          <t>02-10-2026 19:00:07</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7190,32 +7182,32 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>110227</v>
+        <v>112332</v>
       </c>
       <c r="C104" t="n">
-        <v>382358</v>
+        <v>388016</v>
       </c>
       <c r="D104" t="n">
-        <v>24515</v>
+        <v>30173</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MARISOL  ACUÑA VAZQUEZ</t>
+          <t>JOSE IGNACIO  AGUIRRE  HERNANDEZ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>03-09-2026 21:18:41</t>
+          <t>02-10-2026 17:08:40</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -7228,26 +7220,26 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>649</v>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M104" t="n">
+        <v>11</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>27-09-2027 17:08:40</t>
+        </is>
+      </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P104" t="n">
-        <v>110080</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
@@ -7255,32 +7247,32 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>112309</v>
+        <v>112364</v>
       </c>
       <c r="C105" t="n">
-        <v>383098</v>
+        <v>215600</v>
       </c>
       <c r="D105" t="n">
-        <v>25255</v>
+        <v>13108</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>BRENDA TAPIA CHAVEZ</t>
+          <t>VERONICA LUCIA ALVAREZ ZAVALA</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>02-10-2026 8:09:50</t>
+          <t>03-10-2026 9:02:37</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -7293,24 +7285,28 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>549</v>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
+        <v>699</v>
+      </c>
+      <c r="M105" t="n">
+        <v>5</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>01-04-2027 9:02:37</t>
+        </is>
+      </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>54458</v>
+      </c>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
@@ -7318,32 +7314,32 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>112311</v>
+        <v>112270</v>
       </c>
       <c r="C106" t="n">
-        <v>387546</v>
+        <v>385596</v>
       </c>
       <c r="D106" t="n">
-        <v>29703</v>
+        <v>27753</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>LUIS FRANCISCO ORTEGA FRANCO</t>
+          <t>LUIS GIOVANNIE GARCIA  HERNADEZ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>02-10-2026 9:43:43</t>
+          <t>01-10-2026 16:55:45</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-01-2027 23:59:59</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -7360,14 +7356,14 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>599</v>
+        <v>1549</v>
       </c>
       <c r="M106" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>31-03-2027 9:43:43</t>
+          <t>26-09-2027 16:55:45</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -7383,32 +7379,32 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>112325</v>
+        <v>112293</v>
       </c>
       <c r="C107" t="n">
-        <v>387751</v>
+        <v>134981</v>
       </c>
       <c r="D107" t="n">
-        <v>29908</v>
+        <v>32629</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MARI CRUZ JUAREZ LOPEZ</t>
+          <t>MARIA FERNANDA  RAMON  DE LA CRUZ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>02-10-2026 13:45:09</t>
+          <t>01-10-2026 19:11:32</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -7425,14 +7421,14 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>849</v>
+        <v>599</v>
       </c>
       <c r="M107" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>27-09-2027 13:45:09</t>
+          <t>30-03-2027 19:11:32</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -7448,27 +7444,27 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>112269</v>
+        <v>112302</v>
       </c>
       <c r="C108" t="n">
-        <v>387844</v>
+        <v>351343</v>
       </c>
       <c r="D108" t="n">
-        <v>30001</v>
+        <v>93507</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>DANIELA MONTSERRAT MARTINEZ  PLASCENCIA</t>
+          <t>ASTRID ESTHEFANY ORGEN  OBESO</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>AZAHARES CUL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>01-10-2026 16:54:08</t>
+          <t>01-10-2026 20:10:26</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7497,7 +7493,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>30-03-2027 16:54:08</t>
+          <t>30-03-2027 20:10:26</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -7513,27 +7509,27 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>112344</v>
+        <v>112336</v>
       </c>
       <c r="C109" t="n">
-        <v>388041</v>
+        <v>172829</v>
       </c>
       <c r="D109" t="n">
-        <v>30198</v>
+        <v>70348</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>DIANA GUADALUPE URIAS RUIZ</t>
+          <t>EVA ELIZABETH ARREOLA LOPEZ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SEND CHIH</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>02-10-2026 17:58:17</t>
+          <t>02-10-2026 17:24:08</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7555,14 +7551,14 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>599</v>
+        <v>549</v>
       </c>
       <c r="M109" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>31-03-2027 17:58:17</t>
+          <t>27-09-2027 17:24:08</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -7578,32 +7574,32 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>111736</v>
+        <v>112238</v>
       </c>
       <c r="C110" t="n">
-        <v>382132</v>
+        <v>36177</v>
       </c>
       <c r="D110" t="n">
-        <v>24289</v>
+        <v>34091</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>DAFNE VALERIA SARABIA  ALTAMIRANO</t>
+          <t>DENISSE  VARGAS MARTINEZZ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>24-09-2026 15:01:07</t>
+          <t>01-10-2026 8:10:41</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>30-10-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -7634,7 +7630,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>109992</v>
+        <v>53295</v>
       </c>
       <c r="Q110" t="inlineStr"/>
     </row>
@@ -7643,32 +7639,32 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>112272</v>
+        <v>112304</v>
       </c>
       <c r="C111" t="n">
-        <v>387850</v>
+        <v>387933</v>
       </c>
       <c r="D111" t="n">
-        <v>30007</v>
+        <v>30090</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>PAMINGER FLORIAN  FLORIAN</t>
+          <t>ALISON ORTEGA GOMEZ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>01-10-2026 16:59:14</t>
+          <t>02-10-2026 6:15:03</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -7685,17 +7681,19 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>799</v>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M111" t="n">
+        <v>11</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>27-09-2027 6:15:03</t>
+        </is>
+      </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P111" t="inlineStr"/>
@@ -7706,27 +7704,27 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>112330</v>
+        <v>112340</v>
       </c>
       <c r="C112" t="n">
-        <v>388014</v>
+        <v>388031</v>
       </c>
       <c r="D112" t="n">
-        <v>30171</v>
+        <v>30188</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FIORENZA GARELLI  LEDESMA</t>
+          <t>JOEL AURELIO  MEJIA  AGUILAR</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>02-10-2026 16:49:48</t>
+          <t>02-10-2026 17:39:50</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7748,14 +7746,14 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>849</v>
+        <v>599</v>
       </c>
       <c r="M112" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>27-09-2027 16:49:48</t>
+          <t>31-03-2027 17:39:50</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -7771,27 +7769,29 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>112324</v>
+        <v>110103</v>
       </c>
       <c r="C113" t="n">
-        <v>387794</v>
-      </c>
-      <c r="D113" t="n">
-        <v>29951</v>
+        <v>202835</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>00343</t>
+        </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ALAN ALI GARCIA MARTINEZ</t>
+          <t>CRISTOBAL TIRADO CASTAÑEDA</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>02-10-2026 13:19:35</t>
+          <t>02-09-2026 11:12:05</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7809,18 +7809,18 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>649</v>
+        <v>499</v>
       </c>
       <c r="M113" t="n">
         <v>11</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>27-09-2027 13:19:35</t>
+          <t>28-08-2027 11:12:05</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -7828,7 +7828,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr"/>
+      <c r="P113" t="n">
+        <v>91359</v>
+      </c>
       <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
@@ -7836,27 +7838,27 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>112235</v>
+        <v>112253</v>
       </c>
       <c r="C114" t="n">
-        <v>387285</v>
+        <v>387797</v>
       </c>
       <c r="D114" t="n">
-        <v>29442</v>
+        <v>29954</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CAMILA CERRILLO ESTRADA</t>
+          <t>JOSHA JANDRY  BELLO  GONZALEZ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>01-10-2026 7:29:03</t>
+          <t>01-10-2026 13:06:16</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7878,17 +7880,19 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>949</v>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
+        <v>649</v>
+      </c>
+      <c r="M114" t="n">
+        <v>11</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>26-09-2027 13:06:16</t>
+        </is>
+      </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P114" t="inlineStr"/>
@@ -7899,27 +7903,27 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>112285</v>
+        <v>112292</v>
       </c>
       <c r="C115" t="n">
-        <v>387877</v>
+        <v>386711</v>
       </c>
       <c r="D115" t="n">
-        <v>30034</v>
+        <v>28868</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GRACIELA VARGAS OCHOA</t>
+          <t>ANA DELIA  LOPEZ  NIEBLAS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>01-10-2026 18:27:20</t>
+          <t>01-10-2026 19:10:21</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7941,17 +7945,19 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>549</v>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M115" t="n">
+        <v>5</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>30-03-2027 19:10:21</t>
+        </is>
+      </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P115" t="inlineStr"/>
@@ -7962,32 +7968,32 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>112249</v>
+        <v>112310</v>
       </c>
       <c r="C116" t="n">
-        <v>387788</v>
+        <v>387950</v>
       </c>
       <c r="D116" t="n">
-        <v>29945</v>
+        <v>30107</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA PIGNI RIMOLDI</t>
+          <t>GABRIEL TREJO CAMACHO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>01-10-2026 11:52:36</t>
+          <t>02-10-2026 8:42:40</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -8004,17 +8010,19 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>799</v>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
+        <v>849</v>
+      </c>
+      <c r="M116" t="n">
+        <v>11</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>27-09-2027 8:42:40</t>
+        </is>
+      </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P116" t="inlineStr"/>
@@ -8025,27 +8033,27 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>112313</v>
+        <v>110104</v>
       </c>
       <c r="C117" t="n">
-        <v>386133</v>
+        <v>129528</v>
       </c>
       <c r="D117" t="n">
-        <v>28290</v>
+        <v>27196</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>LAURA LETICIA ESPARZA MARTINEZ</t>
+          <t>MARCO ANTONIO BARRAZA  PAREDES</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SEND CHIH</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>02-10-2026 10:20:26</t>
+          <t>02-09-2026 11:17:33</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8063,24 +8071,28 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>949</v>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
+        <v>399</v>
+      </c>
+      <c r="M117" t="n">
+        <v>11</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>28-08-2027 11:17:33</t>
+        </is>
+      </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>66241</v>
+      </c>
       <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
@@ -8088,32 +8100,34 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>112252</v>
+        <v>111397</v>
       </c>
       <c r="C118" t="n">
-        <v>200980</v>
-      </c>
-      <c r="D118" t="n">
-        <v>98487</v>
+        <v>361169</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>03334</t>
+        </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>JOSE ARTURO HURTADO ESQUER</t>
+          <t>SONIA LOPEZ  RUIZ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>01-10-2026 12:52:41</t>
+          <t>21-09-2026 17:26:29</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>03-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -8130,23 +8144,21 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>699</v>
-      </c>
-      <c r="M118" t="n">
-        <v>5</v>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>30-03-2027 12:52:41</t>
-        </is>
-      </c>
+        <v>799</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>10528</v>
+        <v>100529</v>
       </c>
       <c r="Q118" t="inlineStr"/>
     </row>
@@ -8155,27 +8167,27 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>112277</v>
+        <v>112258</v>
       </c>
       <c r="C119" t="n">
-        <v>387864</v>
+        <v>350328</v>
       </c>
       <c r="D119" t="n">
-        <v>30021</v>
+        <v>92492</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>JESUS JULIAN GALLEGOS HERREEA</t>
+          <t>PAMELA RODRIGUEZ N</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>01-10-2026 17:42:25</t>
+          <t>01-10-2026 14:03:38</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8197,14 +8209,14 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M119" t="n">
         <v>11</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>26-09-2027 17:42:25</t>
+          <t>26-09-2027 14:03:38</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -8220,27 +8232,27 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>112284</v>
+        <v>112294</v>
       </c>
       <c r="C120" t="n">
-        <v>387872</v>
+        <v>387904</v>
       </c>
       <c r="D120" t="n">
-        <v>30029</v>
+        <v>30061</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>MONSERRAT  SAVAAVEDRA  ROJAS</t>
+          <t>LAISHA AMAIRAMI DOMINGUEZ GARCIA</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>SAN ISIDRO CUL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>01-10-2026 18:20:28</t>
+          <t>01-10-2026 19:16:44</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8262,7 +8274,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>549</v>
+        <v>699</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -8283,32 +8295,32 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>112318</v>
+        <v>112337</v>
       </c>
       <c r="C121" t="n">
-        <v>387972</v>
+        <v>388027</v>
       </c>
       <c r="D121" t="n">
-        <v>30129</v>
+        <v>30184</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>NANCY  REMIGIO ARZATE</t>
+          <t>MARTHA KARINA LOPEZ  ALQUICIRA</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>02-10-2026 11:31:57</t>
+          <t>02-10-2026 17:30:59</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>02-01-2027 23:59:59</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -8325,14 +8337,14 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>699</v>
+        <v>1549</v>
       </c>
       <c r="M121" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>31-03-2027 11:31:57</t>
+          <t>27-09-2027 17:30:59</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -8348,27 +8360,27 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>112234</v>
+        <v>112280</v>
       </c>
       <c r="C122" t="n">
-        <v>386565</v>
+        <v>125817</v>
       </c>
       <c r="D122" t="n">
-        <v>28722</v>
+        <v>23492</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>JOSE ARMANDO BARAJAS GONGORA</t>
+          <t>ALEJANDRO  ARREDONDO BOJORQUEZ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>01-10-2026 6:16:40</t>
+          <t>01-10-2026 18:03:34</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8386,11 +8398,11 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>949</v>
+        <v>699</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -8403,7 +8415,9 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr"/>
+      <c r="P122" t="n">
+        <v>43718</v>
+      </c>
       <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
@@ -8411,32 +8425,34 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>112301</v>
+        <v>112347</v>
       </c>
       <c r="C123" t="n">
-        <v>157985</v>
-      </c>
-      <c r="D123" t="n">
-        <v>55528</v>
+        <v>104900</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>02647</t>
+        </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>JOHANA JAQUELINE RAMOS ELIZALDE</t>
+          <t>JORGE VALENCIA CALDERON</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>01-10-2026 20:07:43</t>
+          <t>02-10-2026 18:35:24</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -8460,7 +8476,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>30-03-2027 20:07:43</t>
+          <t>31-03-2027 18:35:24</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -8469,7 +8485,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>68615</v>
+        <v>73428</v>
       </c>
       <c r="Q123" t="inlineStr"/>
     </row>
@@ -8478,32 +8494,34 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>112358</v>
+        <v>112113</v>
       </c>
       <c r="C124" t="n">
-        <v>387752</v>
-      </c>
-      <c r="D124" t="n">
-        <v>29909</v>
+        <v>361486</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>03651</t>
+        </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL JUAREZ TLECUILE</t>
+          <t>MARIANA MORALES  CRUZ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>03-10-2026 6:46:36</t>
+          <t>29-09-2026 18:53:22</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>04-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -8516,26 +8534,26 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>599</v>
-      </c>
-      <c r="M124" t="n">
-        <v>5</v>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>01-04-2027 6:46:36</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P124" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>100650</v>
+      </c>
       <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
@@ -8543,32 +8561,32 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>110534</v>
+        <v>112249</v>
       </c>
       <c r="C125" t="n">
-        <v>376238</v>
+        <v>387788</v>
       </c>
       <c r="D125" t="n">
-        <v>18398</v>
+        <v>29945</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RUBEN ALBERTO  GUIZAR  CAMACHO</t>
+          <t>MARIA FERNANDA PIGNI RIMOLDI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>08-09-2026 20:16:38</t>
+          <t>01-10-2026 11:52:36</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>28-10-2026 23:59:59</t>
+          <t>01-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -8581,11 +8599,11 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>599</v>
+        <v>799</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -8598,9 +8616,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P125" t="n">
-        <v>107294</v>
-      </c>
+      <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
@@ -8608,17 +8624,17 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>112355</v>
+        <v>112313</v>
       </c>
       <c r="C126" t="n">
-        <v>386769</v>
+        <v>386133</v>
       </c>
       <c r="D126" t="n">
-        <v>28926</v>
+        <v>28290</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ALEXA DE MARIA SOTO  CHAVEZ</t>
+          <t>LAURA LETICIA ESPARZA MARTINEZ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -8628,12 +8644,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>03-10-2026 6:06:53</t>
+          <t>02-10-2026 10:20:26</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>03-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -8650,19 +8666,17 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>849</v>
-      </c>
-      <c r="M126" t="n">
-        <v>11</v>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>28-09-2027 6:06:53</t>
-        </is>
-      </c>
+        <v>949</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P126" t="inlineStr"/>
@@ -8673,17 +8687,17 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>112247</v>
+        <v>112234</v>
       </c>
       <c r="C127" t="n">
-        <v>387785</v>
+        <v>386565</v>
       </c>
       <c r="D127" t="n">
-        <v>29942</v>
+        <v>28722</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>GERARDO GONZALEZ REBOLLOSO</t>
+          <t>JOSE ARMANDO BARAJAS GONGORA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -8693,7 +8707,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>01-10-2026 11:33:27</t>
+          <t>01-10-2026 6:16:40</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8736,32 +8750,32 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>112297</v>
+        <v>112324</v>
       </c>
       <c r="C128" t="n">
-        <v>347840</v>
+        <v>387794</v>
       </c>
       <c r="D128" t="n">
-        <v>90005</v>
+        <v>29951</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SANTIAGO LOPEZ MALVAEZ</t>
+          <t>ALAN ALI GARCIA MARTINEZ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>01-10-2026 19:25:55</t>
+          <t>02-10-2026 13:19:35</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01-11-2026 23:59:59</t>
+          <t>02-11-2026 23:59:59</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -8778,14 +8792,14 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>599</v>
+        <v>649</v>
       </c>
       <c r="M128" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>30-03-2027 19:25:55</t>
+          <t>27-09-2027 13:19:35</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -8801,32 +8815,32 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>112316</v>
+        <v>110534</v>
       </c>
       <c r="C129" t="n">
-        <v>387965</v>
+        <v>376238</v>
       </c>
       <c r="D129" t="n">
-        <v>30122</v>
+        <v>18398</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>MARIEL LETICIA  MACIAS  ROMAN</t>
+          <t>RUBEN ALBERTO  GUIZAR  CAMACHO</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>02-10-2026 11:00:28</t>
+          <t>08-09-2026 20:16:38</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>02-11-2026 23:59:59</t>
+          <t>28-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -8839,26 +8853,26 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>699</v>
-      </c>
-      <c r="M129" t="n">
-        <v>5</v>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>31-03-2027 11:00:28</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P129" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>107294</v>
+      </c>
       <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
@@ -8866,90 +8880,998 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
+        <v>112355</v>
+      </c>
+      <c r="C130" t="n">
+        <v>386769</v>
+      </c>
+      <c r="D130" t="n">
+        <v>28926</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ALEXA DE MARIA SOTO  CHAVEZ</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>03-10-2026 6:06:53</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>03-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>849</v>
+      </c>
+      <c r="M130" t="n">
+        <v>11</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>28-09-2027 6:06:53</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>110203</v>
+      </c>
+      <c r="C131" t="n">
+        <v>348542</v>
+      </c>
+      <c r="D131" t="n">
+        <v>90707</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>JOSEFINA GARCIA GARCIA</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>03-09-2026 17:56:59</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>04-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>649</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>95962</v>
+      </c>
+      <c r="Q131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>112252</v>
+      </c>
+      <c r="C132" t="n">
+        <v>200980</v>
+      </c>
+      <c r="D132" t="n">
+        <v>98487</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>JOSE ARTURO HURTADO ESQUER</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>01-10-2026 12:52:41</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>699</v>
+      </c>
+      <c r="M132" t="n">
+        <v>5</v>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>30-03-2027 12:52:41</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>10528</v>
+      </c>
+      <c r="Q132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>112277</v>
+      </c>
+      <c r="C133" t="n">
+        <v>387864</v>
+      </c>
+      <c r="D133" t="n">
+        <v>30021</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>JESUS JULIAN GALLEGOS HERREEA</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>01-10-2026 17:42:25</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>549</v>
+      </c>
+      <c r="M133" t="n">
+        <v>11</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>26-09-2027 17:42:25</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>112284</v>
+      </c>
+      <c r="C134" t="n">
+        <v>387872</v>
+      </c>
+      <c r="D134" t="n">
+        <v>30029</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>MONSERRAT  SAVAAVEDRA  ROJAS</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>01-10-2026 18:20:28</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>549</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>112318</v>
+      </c>
+      <c r="C135" t="n">
+        <v>387972</v>
+      </c>
+      <c r="D135" t="n">
+        <v>30129</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>NANCY  REMIGIO ARZATE</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>02-10-2026 11:31:57</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>699</v>
+      </c>
+      <c r="M135" t="n">
+        <v>5</v>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>31-03-2027 11:31:57</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>110245</v>
+      </c>
+      <c r="C136" t="n">
+        <v>119985</v>
+      </c>
+      <c r="D136" t="n">
+        <v>17692</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>JORGE INZUNZA LOPEZ</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>04-09-2026 12:04:32</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>04-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>399</v>
+      </c>
+      <c r="M136" t="n">
+        <v>11</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>30-08-2027 12:04:32</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>62688</v>
+      </c>
+      <c r="Q136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>112235</v>
+      </c>
+      <c r="C137" t="n">
+        <v>387285</v>
+      </c>
+      <c r="D137" t="n">
+        <v>29442</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>CAMILA CERRILLO ESTRADA</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>01-10-2026 7:29:03</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>949</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>112285</v>
+      </c>
+      <c r="C138" t="n">
+        <v>387877</v>
+      </c>
+      <c r="D138" t="n">
+        <v>30034</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>GRACIELA VARGAS OCHOA</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>01-10-2026 18:27:20</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>549</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>112301</v>
+      </c>
+      <c r="C139" t="n">
+        <v>157985</v>
+      </c>
+      <c r="D139" t="n">
+        <v>55528</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>JOHANA JAQUELINE RAMOS ELIZALDE</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>01-10-2026 20:07:43</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>699</v>
+      </c>
+      <c r="M139" t="n">
+        <v>5</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>30-03-2027 20:07:43</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>68615</v>
+      </c>
+      <c r="Q139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>112358</v>
+      </c>
+      <c r="C140" t="n">
+        <v>387752</v>
+      </c>
+      <c r="D140" t="n">
+        <v>29909</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL JUAREZ TLECUILE</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>03-10-2026 6:46:36</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>03-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>599</v>
+      </c>
+      <c r="M140" t="n">
+        <v>5</v>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>01-04-2027 6:46:36</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>112247</v>
+      </c>
+      <c r="C141" t="n">
+        <v>387785</v>
+      </c>
+      <c r="D141" t="n">
+        <v>29942</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>GERARDO GONZALEZ REBOLLOSO</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>01-10-2026 11:33:27</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>949</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>112297</v>
+      </c>
+      <c r="C142" t="n">
+        <v>347840</v>
+      </c>
+      <c r="D142" t="n">
+        <v>90005</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>SANTIAGO LOPEZ MALVAEZ</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>01-10-2026 19:25:55</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>01-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>599</v>
+      </c>
+      <c r="M142" t="n">
+        <v>5</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>30-03-2027 19:25:55</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>112316</v>
+      </c>
+      <c r="C143" t="n">
+        <v>387965</v>
+      </c>
+      <c r="D143" t="n">
+        <v>30122</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>MARIEL LETICIA  MACIAS  ROMAN</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>02-10-2026 11:00:28</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>02-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>699</v>
+      </c>
+      <c r="M143" t="n">
+        <v>5</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>31-03-2027 11:00:28</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
         <v>112366</v>
       </c>
-      <c r="C130" t="n">
+      <c r="C144" t="n">
         <v>173672</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D144" t="n">
         <v>71180</v>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>AXEL  JIMENEZ MARTINEZ</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>IXTAPALUCA</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>03-10-2026 10:17:50</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H144" t="inlineStr">
         <is>
           <t>03-11-2026 23:59:59</t>
         </is>
       </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Sin filtro</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>RENOVACIÓN</t>
         </is>
       </c>
-      <c r="L130" t="n">
+      <c r="L144" t="n">
         <v>699</v>
       </c>
-      <c r="M130" t="n">
+      <c r="M144" t="n">
         <v>5</v>
       </c>
-      <c r="N130" t="inlineStr">
+      <c r="N144" t="inlineStr">
         <is>
           <t>01-04-2027 10:17:50</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr">
+      <c r="O144" t="inlineStr">
         <is>
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P130" t="n">
+      <c r="P144" t="n">
         <v>80355</v>
       </c>
-      <c r="Q130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Reporte generado: 03-10-2026 06:39 p. m.</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Reporte generado: 04-10-2026 06:37 p. m.</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
